--- a/pokedisplay.xlsx
+++ b/pokedisplay.xlsx
@@ -1806,33 +1806,15 @@
       <c r="AH5" s="32">
         <v>2100.0</v>
       </c>
-      <c r="AI5" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ5" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK5" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL5" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM5" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN5" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO5" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP5" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ5" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI5" s="22"/>
+      <c r="AJ5" s="22"/>
+      <c r="AK5" s="22"/>
+      <c r="AL5" s="22"/>
+      <c r="AM5" s="22"/>
+      <c r="AN5" s="22"/>
+      <c r="AO5" s="22"/>
+      <c r="AP5" s="22"/>
+      <c r="AQ5" s="22"/>
       <c r="AR5" s="33" t="s">
         <v>40</v>
       </c>
@@ -1910,33 +1892,15 @@
       <c r="AH6" s="32">
         <v>3000.0</v>
       </c>
-      <c r="AI6" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ6" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK6" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL6" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM6" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN6" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO6" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP6" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ6" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI6" s="22"/>
+      <c r="AJ6" s="22"/>
+      <c r="AK6" s="22"/>
+      <c r="AL6" s="22"/>
+      <c r="AM6" s="22"/>
+      <c r="AN6" s="22"/>
+      <c r="AO6" s="22"/>
+      <c r="AP6" s="22"/>
+      <c r="AQ6" s="22"/>
       <c r="AR6" s="33" t="s">
         <v>44</v>
       </c>
@@ -2014,33 +1978,15 @@
       <c r="AH7" s="32">
         <v>1800.0</v>
       </c>
-      <c r="AI7" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ7" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK7" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL7" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM7" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN7" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO7" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP7" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ7" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI7" s="22"/>
+      <c r="AJ7" s="22"/>
+      <c r="AK7" s="22"/>
+      <c r="AL7" s="22"/>
+      <c r="AM7" s="22"/>
+      <c r="AN7" s="22"/>
+      <c r="AO7" s="22"/>
+      <c r="AP7" s="22"/>
+      <c r="AQ7" s="22"/>
       <c r="AR7" s="33" t="s">
         <v>48</v>
       </c>
@@ -2118,33 +2064,15 @@
       <c r="AH8" s="32">
         <v>1100.0</v>
       </c>
-      <c r="AI8" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ8" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK8" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL8" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM8" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN8" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO8" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP8" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ8" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI8" s="22"/>
+      <c r="AJ8" s="22"/>
+      <c r="AK8" s="22"/>
+      <c r="AL8" s="22"/>
+      <c r="AM8" s="22"/>
+      <c r="AN8" s="22"/>
+      <c r="AO8" s="22"/>
+      <c r="AP8" s="22"/>
+      <c r="AQ8" s="22"/>
       <c r="AR8" s="33" t="s">
         <v>52</v>
       </c>
@@ -2222,33 +2150,15 @@
       <c r="AH9" s="46">
         <v>600.0</v>
       </c>
-      <c r="AI9" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ9" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK9" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL9" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM9" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN9" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO9" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP9" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ9" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI9" s="22"/>
+      <c r="AJ9" s="22"/>
+      <c r="AK9" s="22"/>
+      <c r="AL9" s="22"/>
+      <c r="AM9" s="22"/>
+      <c r="AN9" s="22"/>
+      <c r="AO9" s="22"/>
+      <c r="AP9" s="22"/>
+      <c r="AQ9" s="22"/>
       <c r="AR9" s="33" t="s">
         <v>56</v>
       </c>
@@ -2330,33 +2240,15 @@
       <c r="AH10" s="32">
         <v>420.0</v>
       </c>
-      <c r="AI10" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ10" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK10" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL10" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM10" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN10" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO10" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP10" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ10" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI10" s="22"/>
+      <c r="AJ10" s="22"/>
+      <c r="AK10" s="22"/>
+      <c r="AL10" s="22"/>
+      <c r="AM10" s="22"/>
+      <c r="AN10" s="22"/>
+      <c r="AO10" s="22"/>
+      <c r="AP10" s="22"/>
+      <c r="AQ10" s="22"/>
       <c r="AR10" s="33" t="s">
         <v>60</v>
       </c>
@@ -2434,33 +2326,15 @@
       <c r="AH11" s="32">
         <v>1150.0</v>
       </c>
-      <c r="AI11" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ11" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK11" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL11" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM11" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN11" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO11" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP11" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ11" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI11" s="22"/>
+      <c r="AJ11" s="22"/>
+      <c r="AK11" s="22"/>
+      <c r="AL11" s="22"/>
+      <c r="AM11" s="22"/>
+      <c r="AN11" s="22"/>
+      <c r="AO11" s="22"/>
+      <c r="AP11" s="22"/>
+      <c r="AQ11" s="22"/>
       <c r="AR11" s="33" t="s">
         <v>64</v>
       </c>
@@ -2540,33 +2414,15 @@
       <c r="AH12" s="32">
         <v>580.0</v>
       </c>
-      <c r="AI12" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ12" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK12" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL12" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM12" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN12" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO12" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP12" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ12" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI12" s="22"/>
+      <c r="AJ12" s="22"/>
+      <c r="AK12" s="22"/>
+      <c r="AL12" s="22"/>
+      <c r="AM12" s="22"/>
+      <c r="AN12" s="22"/>
+      <c r="AO12" s="22"/>
+      <c r="AP12" s="22"/>
+      <c r="AQ12" s="22"/>
       <c r="AR12" s="33" t="s">
         <v>68</v>
       </c>
@@ -2646,33 +2502,15 @@
       <c r="AH13" s="32">
         <v>380.0</v>
       </c>
-      <c r="AI13" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ13" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK13" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL13" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM13" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN13" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO13" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP13" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ13" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI13" s="22"/>
+      <c r="AJ13" s="22"/>
+      <c r="AK13" s="22"/>
+      <c r="AL13" s="22"/>
+      <c r="AM13" s="22"/>
+      <c r="AN13" s="22"/>
+      <c r="AO13" s="22"/>
+      <c r="AP13" s="22"/>
+      <c r="AQ13" s="22"/>
       <c r="AR13" s="33" t="s">
         <v>72</v>
       </c>
@@ -2750,33 +2588,15 @@
       <c r="AH14" s="32">
         <v>280.0</v>
       </c>
-      <c r="AI14" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ14" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK14" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL14" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM14" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN14" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO14" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP14" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ14" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI14" s="22"/>
+      <c r="AJ14" s="22"/>
+      <c r="AK14" s="22"/>
+      <c r="AL14" s="22"/>
+      <c r="AM14" s="22"/>
+      <c r="AN14" s="22"/>
+      <c r="AO14" s="22"/>
+      <c r="AP14" s="22"/>
+      <c r="AQ14" s="22"/>
       <c r="AR14" s="33" t="s">
         <v>76</v>
       </c>
@@ -2856,33 +2676,15 @@
       <c r="AH15" s="32">
         <v>420.0</v>
       </c>
-      <c r="AI15" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ15" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK15" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL15" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM15" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN15" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO15" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP15" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ15" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI15" s="22"/>
+      <c r="AJ15" s="22"/>
+      <c r="AK15" s="22"/>
+      <c r="AL15" s="22"/>
+      <c r="AM15" s="22"/>
+      <c r="AN15" s="22"/>
+      <c r="AO15" s="22"/>
+      <c r="AP15" s="22"/>
+      <c r="AQ15" s="22"/>
       <c r="AR15" s="33" t="s">
         <v>80</v>
       </c>
@@ -2962,33 +2764,15 @@
       <c r="AH16" s="32">
         <v>330.0</v>
       </c>
-      <c r="AI16" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ16" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK16" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL16" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM16" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN16" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO16" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP16" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ16" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI16" s="22"/>
+      <c r="AJ16" s="22"/>
+      <c r="AK16" s="22"/>
+      <c r="AL16" s="22"/>
+      <c r="AM16" s="22"/>
+      <c r="AN16" s="22"/>
+      <c r="AO16" s="22"/>
+      <c r="AP16" s="22"/>
+      <c r="AQ16" s="22"/>
       <c r="AR16" s="33" t="s">
         <v>84</v>
       </c>
@@ -3070,33 +2854,15 @@
       <c r="AH17" s="32">
         <v>215.0</v>
       </c>
-      <c r="AI17" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ17" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK17" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL17" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM17" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN17" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO17" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP17" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ17" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI17" s="22"/>
+      <c r="AJ17" s="22"/>
+      <c r="AK17" s="22"/>
+      <c r="AL17" s="22"/>
+      <c r="AM17" s="22"/>
+      <c r="AN17" s="22"/>
+      <c r="AO17" s="22"/>
+      <c r="AP17" s="22"/>
+      <c r="AQ17" s="22"/>
       <c r="AR17" s="33" t="s">
         <v>90</v>
       </c>
@@ -3176,33 +2942,15 @@
       <c r="AH18" s="32">
         <v>220.0</v>
       </c>
-      <c r="AI18" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ18" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK18" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL18" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM18" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN18" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO18" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP18" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ18" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI18" s="22"/>
+      <c r="AJ18" s="22"/>
+      <c r="AK18" s="22"/>
+      <c r="AL18" s="22"/>
+      <c r="AM18" s="22"/>
+      <c r="AN18" s="22"/>
+      <c r="AO18" s="22"/>
+      <c r="AP18" s="22"/>
+      <c r="AQ18" s="22"/>
       <c r="AR18" s="33" t="s">
         <v>94</v>
       </c>
@@ -3282,33 +3030,15 @@
       <c r="AH19" s="32">
         <v>220.0</v>
       </c>
-      <c r="AI19" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ19" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK19" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL19" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM19" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN19" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO19" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP19" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ19" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI19" s="22"/>
+      <c r="AJ19" s="22"/>
+      <c r="AK19" s="22"/>
+      <c r="AL19" s="22"/>
+      <c r="AM19" s="22"/>
+      <c r="AN19" s="22"/>
+      <c r="AO19" s="22"/>
+      <c r="AP19" s="22"/>
+      <c r="AQ19" s="22"/>
       <c r="AR19" s="33" t="s">
         <v>98</v>
       </c>
@@ -3388,33 +3118,15 @@
       <c r="AH20" s="32">
         <v>245.0</v>
       </c>
-      <c r="AI20" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ20" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK20" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL20" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM20" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN20" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO20" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP20" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ20" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI20" s="22"/>
+      <c r="AJ20" s="22"/>
+      <c r="AK20" s="22"/>
+      <c r="AL20" s="22"/>
+      <c r="AM20" s="22"/>
+      <c r="AN20" s="22"/>
+      <c r="AO20" s="22"/>
+      <c r="AP20" s="22"/>
+      <c r="AQ20" s="22"/>
       <c r="AR20" s="33" t="s">
         <v>102</v>
       </c>
@@ -3498,33 +3210,15 @@
       <c r="AH21" s="32">
         <v>245.0</v>
       </c>
-      <c r="AI21" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ21" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK21" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL21" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM21" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN21" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO21" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP21" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ21" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI21" s="22"/>
+      <c r="AJ21" s="22"/>
+      <c r="AK21" s="22"/>
+      <c r="AL21" s="22"/>
+      <c r="AM21" s="22"/>
+      <c r="AN21" s="22"/>
+      <c r="AO21" s="22"/>
+      <c r="AP21" s="22"/>
+      <c r="AQ21" s="22"/>
       <c r="AR21" s="33" t="s">
         <v>106</v>
       </c>
@@ -3612,33 +3306,15 @@
       <c r="AH22" s="32">
         <v>205.0</v>
       </c>
-      <c r="AI22" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ22" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK22" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL22" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM22" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN22" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO22" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP22" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ22" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI22" s="22"/>
+      <c r="AJ22" s="22"/>
+      <c r="AK22" s="22"/>
+      <c r="AL22" s="22"/>
+      <c r="AM22" s="22"/>
+      <c r="AN22" s="22"/>
+      <c r="AO22" s="22"/>
+      <c r="AP22" s="22"/>
+      <c r="AQ22" s="22"/>
       <c r="AR22" s="33" t="s">
         <v>110</v>
       </c>
@@ -3732,33 +3408,15 @@
       <c r="AH23" s="32">
         <v>200.0</v>
       </c>
-      <c r="AI23" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ23" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK23" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL23" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM23" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN23" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO23" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP23" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ23" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI23" s="22"/>
+      <c r="AJ23" s="22"/>
+      <c r="AK23" s="22"/>
+      <c r="AL23" s="22"/>
+      <c r="AM23" s="22"/>
+      <c r="AN23" s="22"/>
+      <c r="AO23" s="22"/>
+      <c r="AP23" s="22"/>
+      <c r="AQ23" s="22"/>
       <c r="AR23" s="33" t="s">
         <v>114</v>
       </c>
@@ -3856,33 +3514,15 @@
       <c r="AH24" s="32">
         <v>210.0</v>
       </c>
-      <c r="AI24" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ24" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK24" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL24" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM24" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN24" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO24" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP24" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ24" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI24" s="22"/>
+      <c r="AJ24" s="22"/>
+      <c r="AK24" s="22"/>
+      <c r="AL24" s="22"/>
+      <c r="AM24" s="22"/>
+      <c r="AN24" s="22"/>
+      <c r="AO24" s="22"/>
+      <c r="AP24" s="22"/>
+      <c r="AQ24" s="22"/>
       <c r="AR24" s="33" t="s">
         <v>118</v>
       </c>
@@ -3990,33 +3630,15 @@
       <c r="AH25" s="32">
         <v>210.0</v>
       </c>
-      <c r="AI25" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ25" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK25" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL25" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM25" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN25" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO25" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP25" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ25" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI25" s="22"/>
+      <c r="AJ25" s="22"/>
+      <c r="AK25" s="22"/>
+      <c r="AL25" s="22"/>
+      <c r="AM25" s="22"/>
+      <c r="AN25" s="22"/>
+      <c r="AO25" s="22"/>
+      <c r="AP25" s="22"/>
+      <c r="AQ25" s="22"/>
       <c r="AR25" s="33" t="s">
         <v>122</v>
       </c>
@@ -4124,33 +3746,15 @@
       <c r="AH26" s="32">
         <v>320.0</v>
       </c>
-      <c r="AI26" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ26" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK26" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL26" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM26" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN26" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO26" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP26" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ26" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI26" s="22"/>
+      <c r="AJ26" s="22"/>
+      <c r="AK26" s="22"/>
+      <c r="AL26" s="22"/>
+      <c r="AM26" s="22"/>
+      <c r="AN26" s="22"/>
+      <c r="AO26" s="22"/>
+      <c r="AP26" s="22"/>
+      <c r="AQ26" s="22"/>
       <c r="AR26" s="33" t="s">
         <v>126</v>
       </c>
@@ -4258,33 +3862,15 @@
       <c r="AH27" s="32">
         <v>250.0</v>
       </c>
-      <c r="AI27" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ27" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK27" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL27" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM27" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN27" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO27" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP27" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ27" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI27" s="22"/>
+      <c r="AJ27" s="22"/>
+      <c r="AK27" s="22"/>
+      <c r="AL27" s="22"/>
+      <c r="AM27" s="22"/>
+      <c r="AN27" s="22"/>
+      <c r="AO27" s="22"/>
+      <c r="AP27" s="22"/>
+      <c r="AQ27" s="22"/>
       <c r="AR27" s="33" t="s">
         <v>130</v>
       </c>
@@ -4392,33 +3978,15 @@
       <c r="AH28" s="32">
         <v>230.0</v>
       </c>
-      <c r="AI28" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ28" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK28" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL28" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM28" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN28" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO28" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP28" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ28" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI28" s="22"/>
+      <c r="AJ28" s="22"/>
+      <c r="AK28" s="22"/>
+      <c r="AL28" s="22"/>
+      <c r="AM28" s="22"/>
+      <c r="AN28" s="22"/>
+      <c r="AO28" s="22"/>
+      <c r="AP28" s="22"/>
+      <c r="AQ28" s="22"/>
       <c r="AR28" s="33" t="s">
         <v>134</v>
       </c>
@@ -4526,33 +4094,15 @@
       <c r="AH29" s="32">
         <v>210.0</v>
       </c>
-      <c r="AI29" s="22">
-        <v>725.0</v>
-      </c>
-      <c r="AJ29" s="22">
-        <v>830.0</v>
-      </c>
-      <c r="AK29" s="22">
-        <v>960.0</v>
-      </c>
-      <c r="AL29" s="22">
-        <v>1320.0</v>
-      </c>
-      <c r="AM29" s="22">
-        <v>1700.0</v>
-      </c>
-      <c r="AN29" s="22">
-        <v>1450.0</v>
-      </c>
-      <c r="AO29" s="22">
-        <v>1200.0</v>
-      </c>
-      <c r="AP29" s="22">
-        <v>1800.0</v>
-      </c>
-      <c r="AQ29" s="22">
-        <v>1950.0</v>
-      </c>
+      <c r="AI29" s="22"/>
+      <c r="AJ29" s="22"/>
+      <c r="AK29" s="22"/>
+      <c r="AL29" s="22"/>
+      <c r="AM29" s="22"/>
+      <c r="AN29" s="22"/>
+      <c r="AO29" s="22"/>
+      <c r="AP29" s="22"/>
+      <c r="AQ29" s="22"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="4"/>

--- a/pokedisplay.xlsx
+++ b/pokedisplay.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="102">
   <si>
     <t>📦 POKEVAULT FR — Displays 36 Boosters · Suivi des prix mensuels 2026</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Display PVC (€)</t>
   </si>
   <si>
-    <t>Display Marché fév. 26 (€)</t>
+    <t>Display Marché mars. 26 (€)</t>
   </si>
   <si>
     <t>Évolution %</t>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>PRIX EBAY sur 30 jours lissé</t>
   </si>
   <si>
     <t>EB02</t>
@@ -314,10 +317,13 @@
     <t>ME03</t>
   </si>
   <si>
-    <t>Tempête Émeraude</t>
+    <t>Équilibre parfait</t>
   </si>
   <si>
-    <t>03/2026</t>
+    <t>ME04</t>
+  </si>
+  <si>
+    <t>Chaos Acendant</t>
   </si>
 </sst>
 </file>
@@ -329,9 +335,9 @@
     <numFmt numFmtId="165" formatCode="#,##0 &quot;€&quot;"/>
     <numFmt numFmtId="166" formatCode="+0.0%;-0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0&quot;€&quot;"/>
-    <numFmt numFmtId="168" formatCode="d/m/yyyy"/>
-    <numFmt numFmtId="169" formatCode="#,##0.00&quot;€&quot;"/>
-    <numFmt numFmtId="170" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="168" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="169" formatCode="d/m/yyyy"/>
+    <numFmt numFmtId="170" formatCode="#,##0.00&quot;€&quot;"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -410,9 +416,9 @@
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="13.0"/>
       <color rgb="FFF0C040"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -431,10 +437,9 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="13.0"/>
-      <color rgb="FFF0C040"/>
-      <name val="Calibri"/>
+      <sz val="9.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
     </font>
     <font>
       <u/>
@@ -631,7 +636,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -650,6 +655,9 @@
     <xf borderId="4" fillId="4" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="5" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="6" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -688,8 +696,8 @@
     <xf borderId="5" fillId="7" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="7" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="9" fillId="6" fontId="14" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="6" fillId="7" fontId="15" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -712,7 +720,7 @@
     <xf borderId="9" fillId="6" fontId="17" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="6" fontId="18" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="6" fontId="18" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="9" fillId="6" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -734,16 +742,13 @@
     <xf borderId="5" fillId="8" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="8" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="6" fillId="8" fontId="15" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="9" fillId="6" fontId="16" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="9" fillId="6" fontId="18" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="6" fontId="14" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="9" fillId="6" fontId="16" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -773,6 +778,12 @@
     <xf borderId="5" fillId="8" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="5" fillId="8" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="7" fontId="5" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -788,16 +799,16 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="23" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="22" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="22" numFmtId="169" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="23" numFmtId="169" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="22" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="22" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="23" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="22" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -1137,7 +1148,7 @@
       <c r="AP3" s="9"/>
       <c r="AQ3" s="9"/>
     </row>
-    <row r="4" ht="30.0" customHeight="1">
+    <row r="4" ht="40.5" customHeight="1">
       <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
@@ -1153,193 +1164,195 @@
       <c r="E4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="13">
         <v>45717.0</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="13">
         <v>45748.0</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4" s="13">
         <v>45778.0</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="13">
         <v>45809.0</v>
       </c>
-      <c r="L4" s="12">
+      <c r="L4" s="13">
         <v>45839.0</v>
       </c>
-      <c r="M4" s="13">
+      <c r="M4" s="14">
         <v>45870.0</v>
       </c>
-      <c r="N4" s="12">
+      <c r="N4" s="13">
         <v>45901.0</v>
       </c>
-      <c r="O4" s="12">
+      <c r="O4" s="13">
         <v>45931.0</v>
       </c>
-      <c r="P4" s="12">
+      <c r="P4" s="13">
         <v>45962.0</v>
       </c>
-      <c r="Q4" s="12">
+      <c r="Q4" s="13">
         <v>45992.0</v>
       </c>
-      <c r="R4" s="14" t="s">
+      <c r="R4" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="S4" s="15" t="s">
+      <c r="S4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="T4" s="16" t="s">
+      <c r="T4" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="U4" s="17" t="s">
+      <c r="U4" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="V4" s="17" t="s">
+      <c r="V4" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="W4" s="17" t="s">
+      <c r="W4" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="X4" s="17" t="s">
+      <c r="X4" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="Y4" s="17" t="s">
+      <c r="Y4" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="Z4" s="17" t="s">
+      <c r="Z4" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="AA4" s="17" t="s">
+      <c r="AA4" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="AB4" s="17" t="s">
+      <c r="AB4" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="AC4" s="17" t="s">
+      <c r="AC4" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="AR4" s="18"/>
+      <c r="AR4" s="19"/>
     </row>
     <row r="5" ht="21.75" customHeight="1">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="24">
         <v>110.0</v>
       </c>
-      <c r="F5" s="24">
-        <v>499.0</v>
-      </c>
-      <c r="G5" s="25">
+      <c r="F5" s="25">
+        <v>2100.0</v>
+      </c>
+      <c r="G5" s="26">
         <v>3.5364</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="27">
         <v>1200.0</v>
       </c>
-      <c r="I5" s="26">
+      <c r="I5" s="27">
         <v>1600.0</v>
       </c>
-      <c r="J5" s="26">
+      <c r="J5" s="27">
         <v>1350.0</v>
       </c>
-      <c r="K5" s="26">
+      <c r="K5" s="27">
         <v>1800.0</v>
       </c>
-      <c r="L5" s="26">
+      <c r="L5" s="27">
         <v>1900.0</v>
       </c>
-      <c r="M5" s="26">
+      <c r="M5" s="27">
         <v>2100.0</v>
       </c>
-      <c r="N5" s="26">
+      <c r="N5" s="27">
         <v>2500.0</v>
       </c>
-      <c r="O5" s="27">
+      <c r="O5" s="28">
         <v>2000.0</v>
       </c>
-      <c r="P5" s="28">
+      <c r="P5" s="29">
         <v>1400.0</v>
       </c>
-      <c r="Q5" s="29">
+      <c r="Q5" s="30">
         <v>2100.0</v>
       </c>
-      <c r="R5" s="30" t="s">
+      <c r="R5" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="S5" s="31" t="s">
+      <c r="S5" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="T5" s="32">
+      <c r="T5" s="25">
         <v>2100.0</v>
       </c>
-      <c r="U5" s="33"/>
-      <c r="V5" s="33"/>
-      <c r="W5" s="33"/>
-      <c r="X5" s="33"/>
-      <c r="Y5" s="33"/>
-      <c r="Z5" s="33"/>
-      <c r="AA5" s="33"/>
-      <c r="AB5" s="33"/>
-      <c r="AC5" s="33"/>
-      <c r="AR5" s="34"/>
+      <c r="U5" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V5" s="34"/>
+      <c r="W5" s="34"/>
+      <c r="X5" s="34"/>
+      <c r="Y5" s="34"/>
+      <c r="Z5" s="34"/>
+      <c r="AA5" s="34"/>
+      <c r="AB5" s="34"/>
+      <c r="AC5" s="34"/>
+      <c r="AR5" s="35"/>
     </row>
     <row r="6" ht="21.75" customHeight="1">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="37" t="s">
+      <c r="B6" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="C6" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="39">
+      <c r="D6" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="40">
         <v>110.0</v>
       </c>
-      <c r="F6" s="40">
-        <v>320.0</v>
+      <c r="F6" s="25">
+        <v>3000.0</v>
       </c>
       <c r="G6" s="41">
         <v>1.9091</v>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="27">
         <v>2900.0</v>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="27">
         <v>2800.0</v>
       </c>
-      <c r="J6" s="26">
+      <c r="J6" s="27">
         <v>2850.0</v>
       </c>
-      <c r="K6" s="26">
+      <c r="K6" s="27">
         <v>2900.0</v>
       </c>
-      <c r="L6" s="26">
+      <c r="L6" s="27">
         <v>2950.0</v>
       </c>
-      <c r="M6" s="26">
+      <c r="M6" s="27">
         <v>3000.0</v>
       </c>
-      <c r="N6" s="26">
+      <c r="N6" s="27">
         <v>3100.0</v>
       </c>
       <c r="O6" s="42">
@@ -1348,70 +1361,72 @@
       <c r="P6" s="42">
         <v>3000.0</v>
       </c>
-      <c r="Q6" s="29" t="s">
+      <c r="Q6" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="R6" s="30" t="s">
+      <c r="R6" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="31" t="s">
+      <c r="S6" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="T6" s="32">
+      <c r="T6" s="25">
         <v>3000.0</v>
       </c>
-      <c r="U6" s="33"/>
-      <c r="V6" s="33"/>
-      <c r="W6" s="33"/>
-      <c r="X6" s="33"/>
-      <c r="Y6" s="33"/>
-      <c r="Z6" s="33"/>
-      <c r="AA6" s="33"/>
-      <c r="AB6" s="33"/>
-      <c r="AC6" s="33"/>
-      <c r="AR6" s="34"/>
+      <c r="U6" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V6" s="34"/>
+      <c r="W6" s="34"/>
+      <c r="X6" s="34"/>
+      <c r="Y6" s="34"/>
+      <c r="Z6" s="34"/>
+      <c r="AA6" s="34"/>
+      <c r="AB6" s="34"/>
+      <c r="AC6" s="34"/>
+      <c r="AR6" s="35"/>
     </row>
     <row r="7" ht="21.75" customHeight="1">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="21" t="s">
+      <c r="B7" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="C7" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="23">
+      <c r="D7" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="24">
         <v>110.0</v>
       </c>
-      <c r="F7" s="24">
-        <v>310.0</v>
-      </c>
-      <c r="G7" s="25">
+      <c r="F7" s="25">
+        <v>1800.0</v>
+      </c>
+      <c r="G7" s="26">
         <v>1.8182</v>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="27">
         <v>950.0</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="27">
         <v>1500.0</v>
       </c>
-      <c r="J7" s="26">
+      <c r="J7" s="27">
         <v>1300.0</v>
       </c>
-      <c r="K7" s="26">
+      <c r="K7" s="27">
         <v>1500.0</v>
       </c>
-      <c r="L7" s="26">
+      <c r="L7" s="27">
         <v>1750.0</v>
       </c>
-      <c r="M7" s="26">
+      <c r="M7" s="27">
         <v>2000.0</v>
       </c>
-      <c r="N7" s="26">
+      <c r="N7" s="27">
         <v>2150.0</v>
       </c>
       <c r="O7" s="42">
@@ -1420,70 +1435,72 @@
       <c r="P7" s="42">
         <v>1800.0</v>
       </c>
-      <c r="Q7" s="29" t="s">
+      <c r="Q7" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="R7" s="30" t="s">
+      <c r="R7" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="S7" s="31" t="s">
+      <c r="S7" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="T7" s="32">
+      <c r="T7" s="25">
         <v>1800.0</v>
       </c>
-      <c r="U7" s="33"/>
-      <c r="V7" s="33"/>
-      <c r="W7" s="33"/>
-      <c r="X7" s="33"/>
-      <c r="Y7" s="33"/>
-      <c r="Z7" s="33"/>
-      <c r="AA7" s="33"/>
-      <c r="AB7" s="33"/>
-      <c r="AC7" s="33"/>
-      <c r="AR7" s="34"/>
+      <c r="U7" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V7" s="34"/>
+      <c r="W7" s="34"/>
+      <c r="X7" s="34"/>
+      <c r="Y7" s="34"/>
+      <c r="Z7" s="34"/>
+      <c r="AA7" s="34"/>
+      <c r="AB7" s="34"/>
+      <c r="AC7" s="34"/>
+      <c r="AR7" s="35"/>
     </row>
     <row r="8" ht="21.75" customHeight="1">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="37" t="s">
+      <c r="B8" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="C8" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="39">
+      <c r="D8" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="40">
         <v>110.0</v>
       </c>
-      <c r="F8" s="40">
-        <v>290.0</v>
+      <c r="F8" s="25">
+        <v>1100.0</v>
       </c>
       <c r="G8" s="41">
         <v>1.6364</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="27">
         <v>900.0</v>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="27">
         <v>1200.0</v>
       </c>
-      <c r="J8" s="26">
+      <c r="J8" s="27">
         <v>1300.0</v>
       </c>
-      <c r="K8" s="26">
+      <c r="K8" s="27">
         <v>1450.0</v>
       </c>
-      <c r="L8" s="26">
+      <c r="L8" s="27">
         <v>1900.0</v>
       </c>
-      <c r="M8" s="26">
+      <c r="M8" s="27">
         <v>2500.0</v>
       </c>
-      <c r="N8" s="26">
+      <c r="N8" s="27">
         <v>1900.0</v>
       </c>
       <c r="O8" s="42">
@@ -1492,70 +1509,72 @@
       <c r="P8" s="42">
         <v>1200.0</v>
       </c>
-      <c r="Q8" s="29">
+      <c r="Q8" s="30">
         <v>1150.0</v>
       </c>
-      <c r="R8" s="30">
+      <c r="R8" s="31">
         <v>1150.0</v>
       </c>
-      <c r="S8" s="30">
+      <c r="S8" s="31">
         <v>1100.0</v>
       </c>
-      <c r="T8" s="32">
+      <c r="T8" s="25">
         <v>1100.0</v>
       </c>
-      <c r="U8" s="33"/>
-      <c r="V8" s="33"/>
-      <c r="W8" s="33"/>
-      <c r="X8" s="33"/>
-      <c r="Y8" s="33"/>
-      <c r="Z8" s="33"/>
-      <c r="AA8" s="33"/>
-      <c r="AB8" s="33"/>
-      <c r="AC8" s="33"/>
-      <c r="AR8" s="34"/>
+      <c r="U8" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V8" s="34"/>
+      <c r="W8" s="34"/>
+      <c r="X8" s="34"/>
+      <c r="Y8" s="34"/>
+      <c r="Z8" s="34"/>
+      <c r="AA8" s="34"/>
+      <c r="AB8" s="34"/>
+      <c r="AC8" s="34"/>
+      <c r="AR8" s="35"/>
     </row>
     <row r="9" ht="21.75" customHeight="1">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="21" t="s">
+      <c r="B9" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="C9" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="23">
+      <c r="D9" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="24">
         <v>110.0</v>
       </c>
-      <c r="F9" s="24">
-        <v>210.0</v>
-      </c>
-      <c r="G9" s="25">
+      <c r="F9" s="43">
+        <v>600.0</v>
+      </c>
+      <c r="G9" s="26">
         <v>0.9091</v>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="27">
         <v>420.0</v>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="27">
         <v>450.0</v>
       </c>
-      <c r="J9" s="26">
+      <c r="J9" s="27">
         <v>490.0</v>
       </c>
-      <c r="K9" s="26">
+      <c r="K9" s="27">
         <v>520.0</v>
       </c>
-      <c r="L9" s="26">
+      <c r="L9" s="27">
         <v>560.0</v>
       </c>
-      <c r="M9" s="26">
+      <c r="M9" s="27">
         <v>600.0</v>
       </c>
-      <c r="N9" s="26">
+      <c r="N9" s="27">
         <v>550.0</v>
       </c>
       <c r="O9" s="42">
@@ -1564,70 +1583,72 @@
       <c r="P9" s="42">
         <v>550.0</v>
       </c>
-      <c r="Q9" s="29">
+      <c r="Q9" s="30">
         <v>500.0</v>
       </c>
-      <c r="R9" s="30">
+      <c r="R9" s="31">
         <v>500.0</v>
       </c>
-      <c r="S9" s="30">
+      <c r="S9" s="31">
         <v>450.0</v>
       </c>
       <c r="T9" s="43">
         <v>600.0</v>
       </c>
-      <c r="U9" s="33"/>
-      <c r="V9" s="33"/>
-      <c r="W9" s="33"/>
-      <c r="X9" s="33"/>
-      <c r="Y9" s="33"/>
-      <c r="Z9" s="33"/>
-      <c r="AA9" s="33"/>
-      <c r="AB9" s="33"/>
-      <c r="AC9" s="33"/>
-      <c r="AR9" s="34"/>
+      <c r="U9" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V9" s="34"/>
+      <c r="W9" s="34"/>
+      <c r="X9" s="34"/>
+      <c r="Y9" s="34"/>
+      <c r="Z9" s="34"/>
+      <c r="AA9" s="34"/>
+      <c r="AB9" s="34"/>
+      <c r="AC9" s="34"/>
+      <c r="AR9" s="35"/>
     </row>
     <row r="10" ht="21.75" customHeight="1">
-      <c r="A10" s="35" t="s">
+      <c r="A10" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="37" t="s">
+      <c r="B10" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="C10" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="39">
+      <c r="D10" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="40">
         <v>110.0</v>
       </c>
-      <c r="F10" s="40">
-        <v>215.0</v>
+      <c r="F10" s="25">
+        <v>420.0</v>
       </c>
       <c r="G10" s="41">
         <v>0.9545</v>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="27">
         <v>400.0</v>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="27">
         <v>420.0</v>
       </c>
-      <c r="J10" s="26">
+      <c r="J10" s="27">
         <v>420.0</v>
       </c>
-      <c r="K10" s="26">
+      <c r="K10" s="27">
         <v>430.0</v>
       </c>
-      <c r="L10" s="26">
+      <c r="L10" s="27">
         <v>450.0</v>
       </c>
-      <c r="M10" s="26">
+      <c r="M10" s="27">
         <v>460.0</v>
       </c>
-      <c r="N10" s="26">
+      <c r="N10" s="27">
         <v>410.0</v>
       </c>
       <c r="O10" s="42">
@@ -1636,142 +1657,146 @@
       <c r="P10" s="42">
         <v>400.0</v>
       </c>
-      <c r="Q10" s="29">
+      <c r="Q10" s="30">
         <v>360.0</v>
       </c>
-      <c r="R10" s="30">
+      <c r="R10" s="31">
         <v>390.0</v>
       </c>
-      <c r="S10" s="30">
+      <c r="S10" s="31">
         <v>400.0</v>
       </c>
-      <c r="T10" s="32">
+      <c r="T10" s="25">
         <v>420.0</v>
       </c>
-      <c r="U10" s="33"/>
-      <c r="V10" s="33"/>
-      <c r="W10" s="33"/>
-      <c r="X10" s="33"/>
-      <c r="Y10" s="33"/>
-      <c r="Z10" s="33"/>
-      <c r="AA10" s="33"/>
-      <c r="AB10" s="33"/>
-      <c r="AC10" s="33"/>
-      <c r="AR10" s="34"/>
+      <c r="U10" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V10" s="34"/>
+      <c r="W10" s="34"/>
+      <c r="X10" s="34"/>
+      <c r="Y10" s="34"/>
+      <c r="Z10" s="34"/>
+      <c r="AA10" s="34"/>
+      <c r="AB10" s="34"/>
+      <c r="AC10" s="34"/>
+      <c r="AR10" s="35"/>
     </row>
     <row r="11" ht="21.75" customHeight="1">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="21" t="s">
+      <c r="B11" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="C11" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="23">
+      <c r="D11" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="24">
         <v>130.0</v>
       </c>
-      <c r="F11" s="24">
-        <v>1380.0</v>
-      </c>
-      <c r="G11" s="25">
+      <c r="F11" s="25">
+        <v>1150.0</v>
+      </c>
+      <c r="G11" s="26">
         <v>9.6154</v>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="27">
         <v>1100.0</v>
       </c>
-      <c r="I11" s="26">
+      <c r="I11" s="27">
         <v>1000.0</v>
       </c>
-      <c r="J11" s="26">
+      <c r="J11" s="27">
         <v>1050.0</v>
       </c>
-      <c r="K11" s="26">
+      <c r="K11" s="27">
         <v>1000.0</v>
       </c>
-      <c r="L11" s="26">
+      <c r="L11" s="27">
         <v>1100.0</v>
       </c>
-      <c r="M11" s="26">
+      <c r="M11" s="27">
         <v>1100.0</v>
       </c>
-      <c r="N11" s="26">
+      <c r="N11" s="27">
         <v>1100.0</v>
       </c>
       <c r="O11" s="42">
         <v>1100.0</v>
       </c>
-      <c r="P11" s="28">
+      <c r="P11" s="29">
         <v>1000.0</v>
       </c>
-      <c r="Q11" s="29">
+      <c r="Q11" s="30">
         <v>1000.0</v>
       </c>
-      <c r="R11" s="30">
+      <c r="R11" s="31">
         <v>1100.0</v>
       </c>
-      <c r="S11" s="30">
+      <c r="S11" s="31">
         <v>1200.0</v>
       </c>
-      <c r="T11" s="32">
+      <c r="T11" s="25">
         <v>1150.0</v>
       </c>
-      <c r="U11" s="33"/>
-      <c r="V11" s="33"/>
-      <c r="W11" s="33"/>
-      <c r="X11" s="33"/>
-      <c r="Y11" s="33"/>
-      <c r="Z11" s="33"/>
-      <c r="AA11" s="33"/>
-      <c r="AB11" s="33"/>
-      <c r="AC11" s="33"/>
-      <c r="AR11" s="34"/>
+      <c r="U11" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V11" s="34"/>
+      <c r="W11" s="34"/>
+      <c r="X11" s="34"/>
+      <c r="Y11" s="34"/>
+      <c r="Z11" s="34"/>
+      <c r="AA11" s="34"/>
+      <c r="AB11" s="34"/>
+      <c r="AC11" s="34"/>
+      <c r="AR11" s="35"/>
     </row>
     <row r="12" ht="21.75" customHeight="1">
-      <c r="A12" s="35" t="s">
+      <c r="A12" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="37" t="s">
+      <c r="B12" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="C12" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="39">
+      <c r="D12" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="40">
         <v>130.0</v>
       </c>
-      <c r="F12" s="40">
-        <v>600.0</v>
+      <c r="F12" s="25">
+        <v>580.0</v>
       </c>
       <c r="G12" s="41">
         <v>3.6154</v>
       </c>
-      <c r="H12" s="26">
+      <c r="H12" s="27">
         <v>400.0</v>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="27">
         <v>420.0</v>
       </c>
-      <c r="J12" s="26">
+      <c r="J12" s="27">
         <v>430.0</v>
       </c>
-      <c r="K12" s="26">
+      <c r="K12" s="27">
         <v>420.0</v>
       </c>
-      <c r="L12" s="26">
+      <c r="L12" s="27">
         <v>450.0</v>
       </c>
-      <c r="M12" s="26">
+      <c r="M12" s="27">
         <v>480.0</v>
       </c>
-      <c r="N12" s="26">
+      <c r="N12" s="27">
         <v>430.0</v>
       </c>
       <c r="O12" s="42">
@@ -1780,70 +1805,72 @@
       <c r="P12" s="42">
         <v>520.0</v>
       </c>
-      <c r="Q12" s="29">
+      <c r="Q12" s="30">
         <v>530.0</v>
       </c>
-      <c r="R12" s="30">
+      <c r="R12" s="31">
         <v>520.0</v>
       </c>
-      <c r="S12" s="30">
+      <c r="S12" s="31">
         <v>550.0</v>
       </c>
-      <c r="T12" s="32">
+      <c r="T12" s="25">
         <v>580.0</v>
       </c>
-      <c r="U12" s="33"/>
-      <c r="V12" s="33"/>
-      <c r="W12" s="33"/>
-      <c r="X12" s="33"/>
-      <c r="Y12" s="33"/>
-      <c r="Z12" s="33"/>
-      <c r="AA12" s="33"/>
-      <c r="AB12" s="33"/>
-      <c r="AC12" s="33"/>
-      <c r="AR12" s="34"/>
+      <c r="U12" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V12" s="34"/>
+      <c r="W12" s="34"/>
+      <c r="X12" s="34"/>
+      <c r="Y12" s="34"/>
+      <c r="Z12" s="34"/>
+      <c r="AA12" s="34"/>
+      <c r="AB12" s="34"/>
+      <c r="AC12" s="34"/>
+      <c r="AR12" s="35"/>
     </row>
     <row r="13" ht="21.75" customHeight="1">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="21" t="s">
+      <c r="B13" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="C13" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="23">
+      <c r="D13" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="24">
         <v>130.0</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="25">
+        <v>380.0</v>
+      </c>
+      <c r="G13" s="26">
+        <v>2.2308</v>
+      </c>
+      <c r="H13" s="27">
         <v>420.0</v>
       </c>
-      <c r="G13" s="25">
-        <v>2.2308</v>
-      </c>
-      <c r="H13" s="26">
+      <c r="I13" s="27">
+        <v>410.0</v>
+      </c>
+      <c r="J13" s="27">
         <v>420.0</v>
       </c>
-      <c r="I13" s="26">
+      <c r="K13" s="27">
         <v>410.0</v>
       </c>
-      <c r="J13" s="26">
-        <v>420.0</v>
-      </c>
-      <c r="K13" s="26">
-        <v>410.0</v>
-      </c>
-      <c r="L13" s="26">
+      <c r="L13" s="27">
         <v>400.0</v>
       </c>
-      <c r="M13" s="26">
+      <c r="M13" s="27">
         <v>400.0</v>
       </c>
-      <c r="N13" s="26">
+      <c r="N13" s="27">
         <v>410.0</v>
       </c>
       <c r="O13" s="42">
@@ -1852,70 +1879,72 @@
       <c r="P13" s="42">
         <v>390.0</v>
       </c>
-      <c r="Q13" s="29">
+      <c r="Q13" s="30">
         <v>370.0</v>
       </c>
-      <c r="R13" s="30">
+      <c r="R13" s="31">
         <v>370.0</v>
       </c>
-      <c r="S13" s="30">
+      <c r="S13" s="31">
         <v>375.0</v>
       </c>
-      <c r="T13" s="32">
+      <c r="T13" s="25">
         <v>380.0</v>
       </c>
-      <c r="U13" s="33"/>
-      <c r="V13" s="33"/>
-      <c r="W13" s="33"/>
-      <c r="X13" s="33"/>
-      <c r="Y13" s="33"/>
-      <c r="Z13" s="33"/>
-      <c r="AA13" s="33"/>
-      <c r="AB13" s="33"/>
-      <c r="AC13" s="33"/>
-      <c r="AR13" s="34"/>
+      <c r="U13" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V13" s="34"/>
+      <c r="W13" s="34"/>
+      <c r="X13" s="34"/>
+      <c r="Y13" s="34"/>
+      <c r="Z13" s="34"/>
+      <c r="AA13" s="34"/>
+      <c r="AB13" s="34"/>
+      <c r="AC13" s="34"/>
+      <c r="AR13" s="35"/>
     </row>
     <row r="14" ht="21.75" customHeight="1">
-      <c r="A14" s="35" t="s">
+      <c r="A14" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="37" t="s">
+      <c r="B14" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="C14" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="39">
+      <c r="D14" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="40">
         <v>130.0</v>
       </c>
-      <c r="F14" s="40">
-        <v>320.0</v>
+      <c r="F14" s="25">
+        <v>280.0</v>
       </c>
       <c r="G14" s="41">
         <v>1.4615</v>
       </c>
-      <c r="H14" s="26">
+      <c r="H14" s="27">
         <v>420.0</v>
       </c>
-      <c r="I14" s="26">
+      <c r="I14" s="27">
         <v>410.0</v>
       </c>
-      <c r="J14" s="26">
+      <c r="J14" s="27">
         <v>390.0</v>
       </c>
-      <c r="K14" s="26">
+      <c r="K14" s="27">
         <v>360.0</v>
       </c>
-      <c r="L14" s="26">
+      <c r="L14" s="27">
         <v>350.0</v>
       </c>
-      <c r="M14" s="26">
+      <c r="M14" s="27">
         <v>340.0</v>
       </c>
-      <c r="N14" s="26">
+      <c r="N14" s="27">
         <v>290.0</v>
       </c>
       <c r="O14" s="42">
@@ -1924,70 +1953,72 @@
       <c r="P14" s="42">
         <v>260.0</v>
       </c>
-      <c r="Q14" s="29">
+      <c r="Q14" s="30">
         <v>250.0</v>
       </c>
-      <c r="R14" s="30">
+      <c r="R14" s="31">
         <v>250.0</v>
       </c>
-      <c r="S14" s="30">
+      <c r="S14" s="31">
         <v>265.0</v>
       </c>
-      <c r="T14" s="32">
+      <c r="T14" s="25">
         <v>280.0</v>
       </c>
-      <c r="U14" s="33"/>
-      <c r="V14" s="33"/>
-      <c r="W14" s="33"/>
-      <c r="X14" s="33"/>
-      <c r="Y14" s="33"/>
-      <c r="Z14" s="33"/>
-      <c r="AA14" s="33"/>
-      <c r="AB14" s="33"/>
-      <c r="AC14" s="33"/>
-      <c r="AR14" s="34"/>
+      <c r="U14" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V14" s="34"/>
+      <c r="W14" s="34"/>
+      <c r="X14" s="34"/>
+      <c r="Y14" s="34"/>
+      <c r="Z14" s="34"/>
+      <c r="AA14" s="34"/>
+      <c r="AB14" s="34"/>
+      <c r="AC14" s="34"/>
+      <c r="AR14" s="35"/>
     </row>
     <row r="15" ht="21.75" customHeight="1">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="21" t="s">
+      <c r="B15" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="C15" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="23">
+      <c r="D15" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="24">
         <v>130.0</v>
       </c>
-      <c r="F15" s="24">
-        <v>400.0</v>
-      </c>
-      <c r="G15" s="25">
+      <c r="F15" s="25">
+        <v>420.0</v>
+      </c>
+      <c r="G15" s="26">
         <v>2.0769</v>
       </c>
-      <c r="H15" s="26">
+      <c r="H15" s="27">
         <v>700.0</v>
       </c>
-      <c r="I15" s="26">
+      <c r="I15" s="27">
         <v>680.0</v>
       </c>
-      <c r="J15" s="26">
+      <c r="J15" s="27">
         <v>690.0</v>
       </c>
-      <c r="K15" s="26">
+      <c r="K15" s="27">
         <v>650.0</v>
       </c>
-      <c r="L15" s="26">
+      <c r="L15" s="27">
         <v>420.0</v>
       </c>
-      <c r="M15" s="26">
+      <c r="M15" s="27">
         <v>300.0</v>
       </c>
-      <c r="N15" s="26">
+      <c r="N15" s="27">
         <v>340.0</v>
       </c>
       <c r="O15" s="42">
@@ -1996,7 +2027,7 @@
       <c r="P15" s="42">
         <v>340.0</v>
       </c>
-      <c r="Q15" s="29">
+      <c r="Q15" s="30">
         <v>385.0</v>
       </c>
       <c r="R15" s="44">
@@ -2005,61 +2036,63 @@
       <c r="S15" s="44">
         <v>400.0</v>
       </c>
-      <c r="T15" s="32">
+      <c r="T15" s="25">
         <v>420.0</v>
       </c>
-      <c r="U15" s="33"/>
-      <c r="V15" s="33"/>
-      <c r="W15" s="33"/>
-      <c r="X15" s="33"/>
-      <c r="Y15" s="33"/>
-      <c r="Z15" s="33"/>
-      <c r="AA15" s="33"/>
-      <c r="AB15" s="33"/>
-      <c r="AC15" s="33"/>
-      <c r="AR15" s="34"/>
+      <c r="U15" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V15" s="34"/>
+      <c r="W15" s="34"/>
+      <c r="X15" s="34"/>
+      <c r="Y15" s="34"/>
+      <c r="Z15" s="34"/>
+      <c r="AA15" s="34"/>
+      <c r="AB15" s="34"/>
+      <c r="AC15" s="34"/>
+      <c r="AR15" s="35"/>
     </row>
     <row r="16" ht="21.75" customHeight="1">
-      <c r="A16" s="35" t="s">
+      <c r="A16" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" s="37" t="s">
+      <c r="B16" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="38" t="s">
+      <c r="C16" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="39">
+      <c r="D16" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="40">
         <v>130.0</v>
       </c>
-      <c r="F16" s="40">
-        <v>320.0</v>
+      <c r="F16" s="25">
+        <v>330.0</v>
       </c>
       <c r="G16" s="41">
         <v>1.4615</v>
       </c>
-      <c r="H16" s="26">
+      <c r="H16" s="27">
         <v>410.0</v>
       </c>
-      <c r="I16" s="26">
+      <c r="I16" s="27">
         <v>400.0</v>
       </c>
-      <c r="J16" s="26">
+      <c r="J16" s="27">
         <v>390.0</v>
       </c>
-      <c r="K16" s="26">
+      <c r="K16" s="27">
         <v>380.0</v>
       </c>
-      <c r="L16" s="26">
+      <c r="L16" s="27">
         <v>350.0</v>
       </c>
-      <c r="M16" s="26">
+      <c r="M16" s="27">
         <v>270.0</v>
       </c>
-      <c r="N16" s="26">
+      <c r="N16" s="27">
         <v>310.0</v>
       </c>
       <c r="O16" s="45">
@@ -2068,49 +2101,51 @@
       <c r="P16" s="42">
         <v>300.0</v>
       </c>
-      <c r="Q16" s="29">
+      <c r="Q16" s="30">
         <v>290.0</v>
       </c>
-      <c r="R16" s="30">
+      <c r="R16" s="31">
         <v>300.0</v>
       </c>
       <c r="S16" s="44">
         <v>320.0</v>
       </c>
-      <c r="T16" s="32">
+      <c r="T16" s="25">
         <v>330.0</v>
       </c>
-      <c r="U16" s="33"/>
-      <c r="V16" s="33"/>
-      <c r="W16" s="33"/>
-      <c r="X16" s="33"/>
-      <c r="Y16" s="33"/>
-      <c r="Z16" s="33"/>
-      <c r="AA16" s="33"/>
-      <c r="AB16" s="33"/>
-      <c r="AC16" s="33"/>
-      <c r="AR16" s="34"/>
+      <c r="U16" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V16" s="34"/>
+      <c r="W16" s="34"/>
+      <c r="X16" s="34"/>
+      <c r="Y16" s="34"/>
+      <c r="Z16" s="34"/>
+      <c r="AA16" s="34"/>
+      <c r="AB16" s="34"/>
+      <c r="AC16" s="34"/>
+      <c r="AR16" s="35"/>
     </row>
     <row r="17" ht="21.75" customHeight="1">
       <c r="A17" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="B17" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="C17" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="E17" s="23">
+      <c r="D17" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="24">
         <v>140.0</v>
       </c>
-      <c r="F17" s="24">
-        <v>250.0</v>
-      </c>
-      <c r="G17" s="25">
+      <c r="F17" s="25">
+        <v>215.0</v>
+      </c>
+      <c r="G17" s="26">
         <v>0.7857</v>
       </c>
       <c r="H17" s="42">
@@ -2122,16 +2157,16 @@
       <c r="J17" s="42">
         <v>210.0</v>
       </c>
-      <c r="K17" s="26">
+      <c r="K17" s="27">
         <v>200.0</v>
       </c>
       <c r="L17" s="42">
         <v>210.0</v>
       </c>
-      <c r="M17" s="26">
+      <c r="M17" s="27">
         <v>220.0</v>
       </c>
-      <c r="N17" s="26">
+      <c r="N17" s="27">
         <v>230.0</v>
       </c>
       <c r="O17" s="42">
@@ -2140,47 +2175,49 @@
       <c r="P17" s="42">
         <v>220.0</v>
       </c>
-      <c r="Q17" s="29">
+      <c r="Q17" s="30">
         <v>215.0</v>
       </c>
       <c r="R17" s="44">
         <v>200.0</v>
       </c>
-      <c r="S17" s="30">
+      <c r="S17" s="31">
         <v>220.0</v>
       </c>
-      <c r="T17" s="32">
+      <c r="T17" s="25">
         <v>215.0</v>
       </c>
-      <c r="U17" s="33"/>
-      <c r="V17" s="33"/>
-      <c r="W17" s="33"/>
-      <c r="X17" s="33"/>
-      <c r="Y17" s="33"/>
-      <c r="Z17" s="33"/>
-      <c r="AA17" s="33"/>
-      <c r="AB17" s="33"/>
-      <c r="AC17" s="33"/>
-      <c r="AR17" s="34"/>
+      <c r="U17" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V17" s="34"/>
+      <c r="W17" s="34"/>
+      <c r="X17" s="34"/>
+      <c r="Y17" s="34"/>
+      <c r="Z17" s="34"/>
+      <c r="AA17" s="34"/>
+      <c r="AB17" s="34"/>
+      <c r="AC17" s="34"/>
+      <c r="AR17" s="35"/>
     </row>
     <row r="18" ht="21.75" customHeight="1">
       <c r="A18" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="38" t="s">
+      <c r="C18" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="E18" s="39">
+      <c r="D18" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="40">
         <v>140.0</v>
       </c>
-      <c r="F18" s="40">
-        <v>270.0</v>
+      <c r="F18" s="25">
+        <v>220.0</v>
       </c>
       <c r="G18" s="41">
         <v>0.9286</v>
@@ -2194,16 +2231,16 @@
       <c r="J18" s="42">
         <v>220.0</v>
       </c>
-      <c r="K18" s="26">
+      <c r="K18" s="27">
         <v>225.0</v>
       </c>
       <c r="L18" s="42">
         <v>230.0</v>
       </c>
-      <c r="M18" s="26">
+      <c r="M18" s="27">
         <v>225.0</v>
       </c>
-      <c r="N18" s="26">
+      <c r="N18" s="27">
         <v>230.0</v>
       </c>
       <c r="O18" s="48">
@@ -2212,49 +2249,51 @@
       <c r="P18" s="42">
         <v>230.0</v>
       </c>
-      <c r="Q18" s="29">
+      <c r="Q18" s="30">
         <v>215.0</v>
       </c>
-      <c r="R18" s="30">
+      <c r="R18" s="31">
         <v>225.0</v>
       </c>
-      <c r="S18" s="30">
+      <c r="S18" s="31">
         <v>215.0</v>
       </c>
-      <c r="T18" s="32">
+      <c r="T18" s="25">
         <v>220.0</v>
       </c>
-      <c r="U18" s="33"/>
-      <c r="V18" s="33"/>
-      <c r="W18" s="33"/>
-      <c r="X18" s="33"/>
-      <c r="Y18" s="33"/>
-      <c r="Z18" s="33"/>
-      <c r="AA18" s="33"/>
-      <c r="AB18" s="33"/>
-      <c r="AC18" s="33"/>
-      <c r="AR18" s="34"/>
+      <c r="U18" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V18" s="34"/>
+      <c r="W18" s="34"/>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="34"/>
+      <c r="Z18" s="34"/>
+      <c r="AA18" s="34"/>
+      <c r="AB18" s="34"/>
+      <c r="AC18" s="34"/>
+      <c r="AR18" s="35"/>
     </row>
     <row r="19" ht="21.75" customHeight="1">
       <c r="A19" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="C19" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="23">
+      <c r="D19" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="24">
         <v>140.0</v>
       </c>
-      <c r="F19" s="24">
-        <v>250.0</v>
-      </c>
-      <c r="G19" s="25">
+      <c r="F19" s="25">
+        <v>220.0</v>
+      </c>
+      <c r="G19" s="26">
         <v>0.7857</v>
       </c>
       <c r="H19" s="42">
@@ -2266,16 +2305,16 @@
       <c r="J19" s="42">
         <v>350.0</v>
       </c>
-      <c r="K19" s="26">
+      <c r="K19" s="27">
         <v>325.0</v>
       </c>
       <c r="L19" s="42">
         <v>300.0</v>
       </c>
-      <c r="M19" s="26">
+      <c r="M19" s="27">
         <v>345.0</v>
       </c>
-      <c r="N19" s="26">
+      <c r="N19" s="27">
         <v>330.0</v>
       </c>
       <c r="O19" s="42">
@@ -2284,47 +2323,49 @@
       <c r="P19" s="42">
         <v>270.0</v>
       </c>
-      <c r="Q19" s="29">
+      <c r="Q19" s="30">
         <v>230.0</v>
       </c>
-      <c r="R19" s="30">
+      <c r="R19" s="31">
         <v>210.0</v>
       </c>
-      <c r="S19" s="30">
+      <c r="S19" s="31">
         <v>240.0</v>
       </c>
-      <c r="T19" s="32">
+      <c r="T19" s="25">
         <v>220.0</v>
       </c>
-      <c r="U19" s="33"/>
-      <c r="V19" s="33"/>
-      <c r="W19" s="33"/>
-      <c r="X19" s="33"/>
-      <c r="Y19" s="33"/>
-      <c r="Z19" s="33"/>
-      <c r="AA19" s="33"/>
-      <c r="AB19" s="33"/>
-      <c r="AC19" s="33"/>
-      <c r="AR19" s="34"/>
+      <c r="U19" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V19" s="34"/>
+      <c r="W19" s="34"/>
+      <c r="X19" s="34"/>
+      <c r="Y19" s="34"/>
+      <c r="Z19" s="34"/>
+      <c r="AA19" s="34"/>
+      <c r="AB19" s="34"/>
+      <c r="AC19" s="34"/>
+      <c r="AR19" s="35"/>
     </row>
     <row r="20" ht="21.75" customHeight="1">
       <c r="A20" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="C20" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="E20" s="39">
+      <c r="D20" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="40">
         <v>140.0</v>
       </c>
-      <c r="F20" s="40">
-        <v>240.0</v>
+      <c r="F20" s="25">
+        <v>245.0</v>
       </c>
       <c r="G20" s="41">
         <v>0.7143</v>
@@ -2338,16 +2379,16 @@
       <c r="J20" s="42">
         <v>225.0</v>
       </c>
-      <c r="K20" s="26">
+      <c r="K20" s="27">
         <v>250.0</v>
       </c>
       <c r="L20" s="42">
         <v>290.0</v>
       </c>
-      <c r="M20" s="26">
+      <c r="M20" s="27">
         <v>275.0</v>
       </c>
-      <c r="N20" s="26">
+      <c r="N20" s="27">
         <v>260.0</v>
       </c>
       <c r="O20" s="42">
@@ -2356,49 +2397,51 @@
       <c r="P20" s="42">
         <v>260.0</v>
       </c>
-      <c r="Q20" s="29">
+      <c r="Q20" s="30">
         <v>250.0</v>
       </c>
-      <c r="R20" s="30">
+      <c r="R20" s="31">
         <v>240.0</v>
       </c>
       <c r="S20" s="44">
         <v>240.0</v>
       </c>
-      <c r="T20" s="32">
+      <c r="T20" s="25">
         <v>245.0</v>
       </c>
-      <c r="U20" s="33"/>
-      <c r="V20" s="33"/>
-      <c r="W20" s="33"/>
-      <c r="X20" s="33"/>
-      <c r="Y20" s="33"/>
-      <c r="Z20" s="33"/>
-      <c r="AA20" s="33"/>
-      <c r="AB20" s="33"/>
-      <c r="AC20" s="33"/>
-      <c r="AR20" s="34"/>
+      <c r="U20" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V20" s="34"/>
+      <c r="W20" s="34"/>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="34"/>
+      <c r="Z20" s="34"/>
+      <c r="AA20" s="34"/>
+      <c r="AB20" s="34"/>
+      <c r="AC20" s="34"/>
+      <c r="AR20" s="35"/>
     </row>
     <row r="21" ht="21.75" customHeight="1">
       <c r="A21" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="C21" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="23">
+      <c r="D21" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="24">
         <v>140.0</v>
       </c>
-      <c r="F21" s="24">
-        <v>230.0</v>
-      </c>
-      <c r="G21" s="25">
+      <c r="F21" s="25">
+        <v>245.0</v>
+      </c>
+      <c r="G21" s="26">
         <v>0.6429</v>
       </c>
       <c r="H21" s="42">
@@ -2410,16 +2453,16 @@
       <c r="J21" s="42">
         <v>230.0</v>
       </c>
-      <c r="K21" s="26">
+      <c r="K21" s="27">
         <v>230.0</v>
       </c>
       <c r="L21" s="42">
         <v>235.0</v>
       </c>
-      <c r="M21" s="26">
+      <c r="M21" s="27">
         <v>265.0</v>
       </c>
-      <c r="N21" s="26">
+      <c r="N21" s="27">
         <v>250.0</v>
       </c>
       <c r="O21" s="42">
@@ -2428,47 +2471,49 @@
       <c r="P21" s="42">
         <v>250.0</v>
       </c>
-      <c r="Q21" s="29">
+      <c r="Q21" s="30">
         <v>240.0</v>
       </c>
-      <c r="R21" s="30">
+      <c r="R21" s="31">
         <v>220.0</v>
       </c>
-      <c r="S21" s="30">
+      <c r="S21" s="31">
         <v>240.0</v>
       </c>
-      <c r="T21" s="32">
+      <c r="T21" s="25">
         <v>245.0</v>
       </c>
-      <c r="U21" s="33"/>
-      <c r="V21" s="33"/>
-      <c r="W21" s="33"/>
-      <c r="X21" s="33"/>
-      <c r="Y21" s="33"/>
-      <c r="Z21" s="33"/>
-      <c r="AA21" s="33"/>
-      <c r="AB21" s="33"/>
-      <c r="AC21" s="33"/>
-      <c r="AR21" s="34"/>
+      <c r="U21" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V21" s="34"/>
+      <c r="W21" s="34"/>
+      <c r="X21" s="34"/>
+      <c r="Y21" s="34"/>
+      <c r="Z21" s="34"/>
+      <c r="AA21" s="34"/>
+      <c r="AB21" s="34"/>
+      <c r="AC21" s="34"/>
+      <c r="AR21" s="35"/>
     </row>
     <row r="22" ht="21.75" customHeight="1">
       <c r="A22" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="C22" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="E22" s="39">
+      <c r="D22" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" s="40">
         <v>140.0</v>
       </c>
-      <c r="F22" s="40">
-        <v>200.0</v>
+      <c r="F22" s="25">
+        <v>205.0</v>
       </c>
       <c r="G22" s="41">
         <v>0.4286</v>
@@ -2482,16 +2527,16 @@
       <c r="J22" s="42">
         <v>200.0</v>
       </c>
-      <c r="K22" s="26">
+      <c r="K22" s="27">
         <v>220.0</v>
       </c>
       <c r="L22" s="42">
         <v>225.0</v>
       </c>
-      <c r="M22" s="26">
+      <c r="M22" s="27">
         <v>220.0</v>
       </c>
-      <c r="N22" s="26">
+      <c r="N22" s="27">
         <v>220.0</v>
       </c>
       <c r="O22" s="42">
@@ -2500,49 +2545,51 @@
       <c r="P22" s="42">
         <v>215.0</v>
       </c>
-      <c r="Q22" s="29">
+      <c r="Q22" s="30">
         <v>200.0</v>
       </c>
-      <c r="R22" s="30">
+      <c r="R22" s="31">
         <v>210.0</v>
       </c>
       <c r="S22" s="44">
         <v>200.0</v>
       </c>
-      <c r="T22" s="32">
+      <c r="T22" s="25">
         <v>205.0</v>
       </c>
-      <c r="U22" s="33"/>
-      <c r="V22" s="33"/>
-      <c r="W22" s="33"/>
-      <c r="X22" s="33"/>
-      <c r="Y22" s="33"/>
-      <c r="Z22" s="33"/>
-      <c r="AA22" s="33"/>
-      <c r="AB22" s="33"/>
-      <c r="AC22" s="33"/>
-      <c r="AR22" s="34"/>
+      <c r="U22" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="34"/>
+      <c r="Z22" s="34"/>
+      <c r="AA22" s="34"/>
+      <c r="AB22" s="34"/>
+      <c r="AC22" s="34"/>
+      <c r="AR22" s="35"/>
     </row>
     <row r="23" ht="21.75" customHeight="1">
       <c r="A23" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="B23" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="C23" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E23" s="23">
+      <c r="D23" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="24">
         <v>140.0</v>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="25">
         <v>200.0</v>
       </c>
-      <c r="G23" s="25">
+      <c r="G23" s="26">
         <v>0.4286</v>
       </c>
       <c r="H23" s="42">
@@ -2554,16 +2601,16 @@
       <c r="J23" s="42">
         <v>200.0</v>
       </c>
-      <c r="K23" s="26">
+      <c r="K23" s="27">
         <v>220.0</v>
       </c>
       <c r="L23" s="42">
         <v>230.0</v>
       </c>
-      <c r="M23" s="26">
+      <c r="M23" s="27">
         <v>220.0</v>
       </c>
-      <c r="N23" s="26">
+      <c r="N23" s="27">
         <v>230.0</v>
       </c>
       <c r="O23" s="49">
@@ -2572,47 +2619,49 @@
       <c r="P23" s="42">
         <v>230.0</v>
       </c>
-      <c r="Q23" s="29">
+      <c r="Q23" s="30">
         <v>220.0</v>
       </c>
-      <c r="R23" s="30">
+      <c r="R23" s="31">
         <v>215.0</v>
       </c>
       <c r="S23" s="44">
         <v>200.0</v>
       </c>
-      <c r="T23" s="32">
+      <c r="T23" s="25">
         <v>200.0</v>
       </c>
-      <c r="U23" s="33"/>
-      <c r="V23" s="33"/>
-      <c r="W23" s="33"/>
-      <c r="X23" s="33"/>
-      <c r="Y23" s="33"/>
-      <c r="Z23" s="33"/>
-      <c r="AA23" s="33"/>
-      <c r="AB23" s="33"/>
-      <c r="AC23" s="33"/>
-      <c r="AR23" s="34"/>
+      <c r="U23" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V23" s="34"/>
+      <c r="W23" s="34"/>
+      <c r="X23" s="34"/>
+      <c r="Y23" s="34"/>
+      <c r="Z23" s="34"/>
+      <c r="AA23" s="34"/>
+      <c r="AB23" s="34"/>
+      <c r="AC23" s="34"/>
+      <c r="AR23" s="35"/>
     </row>
     <row r="24" ht="21.75" customHeight="1">
       <c r="A24" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="D24" s="38" t="s">
+      <c r="C24" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="E24" s="39">
+      <c r="D24" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="40">
         <v>140.0</v>
       </c>
-      <c r="F24" s="40">
-        <v>230.0</v>
+      <c r="F24" s="25">
+        <v>210.0</v>
       </c>
       <c r="G24" s="41">
         <v>0.6429</v>
@@ -2626,67 +2675,69 @@
       <c r="J24" s="42">
         <v>240.0</v>
       </c>
-      <c r="K24" s="26">
+      <c r="K24" s="27">
         <v>240.0</v>
       </c>
       <c r="L24" s="42">
         <v>245.0</v>
       </c>
-      <c r="M24" s="26">
+      <c r="M24" s="27">
         <v>260.0</v>
       </c>
-      <c r="N24" s="26">
+      <c r="N24" s="27">
         <v>260.0</v>
       </c>
-      <c r="O24" s="26">
+      <c r="O24" s="27">
         <v>240.0</v>
       </c>
       <c r="P24" s="42">
         <v>225.0</v>
       </c>
-      <c r="Q24" s="29">
+      <c r="Q24" s="30">
         <v>220.0</v>
       </c>
-      <c r="R24" s="30">
+      <c r="R24" s="31">
         <v>210.0</v>
       </c>
-      <c r="S24" s="30">
+      <c r="S24" s="31">
         <v>210.0</v>
       </c>
-      <c r="T24" s="32">
+      <c r="T24" s="25">
         <v>210.0</v>
       </c>
-      <c r="U24" s="33"/>
-      <c r="V24" s="33"/>
-      <c r="W24" s="33"/>
-      <c r="X24" s="33"/>
-      <c r="Y24" s="33"/>
-      <c r="Z24" s="33"/>
-      <c r="AA24" s="33"/>
-      <c r="AB24" s="33"/>
-      <c r="AC24" s="33"/>
-      <c r="AR24" s="34"/>
+      <c r="U24" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V24" s="34"/>
+      <c r="W24" s="34"/>
+      <c r="X24" s="34"/>
+      <c r="Y24" s="34"/>
+      <c r="Z24" s="34"/>
+      <c r="AA24" s="34"/>
+      <c r="AB24" s="34"/>
+      <c r="AC24" s="34"/>
+      <c r="AR24" s="35"/>
     </row>
     <row r="25" ht="21.75" customHeight="1">
       <c r="A25" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="C25" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="C25" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="E25" s="23">
+      <c r="D25" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="24">
         <v>140.0</v>
       </c>
-      <c r="F25" s="24">
-        <v>220.0</v>
-      </c>
-      <c r="G25" s="25">
+      <c r="F25" s="25">
+        <v>210.0</v>
+      </c>
+      <c r="G25" s="26">
         <v>0.5714</v>
       </c>
       <c r="H25" s="42">
@@ -2698,348 +2749,408 @@
       <c r="J25" s="42">
         <v>240.0</v>
       </c>
-      <c r="K25" s="26">
+      <c r="K25" s="27">
         <v>230.0</v>
       </c>
       <c r="L25" s="42">
         <v>220.0</v>
       </c>
-      <c r="M25" s="26">
+      <c r="M25" s="27">
         <v>210.0</v>
       </c>
-      <c r="N25" s="26">
+      <c r="N25" s="27">
         <v>190.0</v>
       </c>
-      <c r="O25" s="26">
+      <c r="O25" s="27">
         <v>200.0</v>
       </c>
       <c r="P25" s="42">
         <v>205.0</v>
       </c>
-      <c r="Q25" s="29">
+      <c r="Q25" s="30">
         <v>210.0</v>
       </c>
-      <c r="R25" s="30">
+      <c r="R25" s="31">
         <v>200.0</v>
       </c>
-      <c r="S25" s="30">
+      <c r="S25" s="31">
         <v>200.0</v>
       </c>
-      <c r="T25" s="32">
+      <c r="T25" s="25">
         <v>210.0</v>
       </c>
-      <c r="U25" s="33"/>
-      <c r="V25" s="33"/>
-      <c r="W25" s="33"/>
-      <c r="X25" s="33"/>
-      <c r="Y25" s="33"/>
-      <c r="Z25" s="33"/>
-      <c r="AA25" s="33"/>
-      <c r="AB25" s="33"/>
-      <c r="AC25" s="33"/>
-      <c r="AR25" s="34"/>
+      <c r="U25" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V25" s="34"/>
+      <c r="W25" s="34"/>
+      <c r="X25" s="34"/>
+      <c r="Y25" s="34"/>
+      <c r="Z25" s="34"/>
+      <c r="AA25" s="34"/>
+      <c r="AB25" s="34"/>
+      <c r="AC25" s="34"/>
+      <c r="AR25" s="35"/>
     </row>
     <row r="26" ht="21.75" customHeight="1">
       <c r="A26" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B26" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="D26" s="38" t="s">
+      <c r="C26" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="E26" s="39">
+      <c r="D26" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" s="40">
         <v>140.0</v>
       </c>
-      <c r="F26" s="40">
-        <v>300.0</v>
+      <c r="F26" s="25">
+        <v>320.0</v>
       </c>
       <c r="G26" s="41">
         <v>1.1429</v>
       </c>
-      <c r="H26" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="I26" s="26" t="s">
-        <v>90</v>
+      <c r="H26" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="I26" s="27" t="s">
+        <v>91</v>
       </c>
       <c r="J26" s="50">
         <v>250.0</v>
       </c>
-      <c r="K26" s="26">
+      <c r="K26" s="27">
         <v>280.0</v>
       </c>
       <c r="L26" s="42">
         <v>305.0</v>
       </c>
-      <c r="M26" s="26">
+      <c r="M26" s="27">
         <v>280.0</v>
       </c>
-      <c r="N26" s="26">
+      <c r="N26" s="27">
         <v>300.0</v>
       </c>
-      <c r="O26" s="26">
+      <c r="O26" s="27">
         <v>320.0</v>
       </c>
       <c r="P26" s="42">
         <v>280.0</v>
       </c>
-      <c r="Q26" s="29">
+      <c r="Q26" s="30">
         <v>290.0</v>
       </c>
-      <c r="R26" s="30">
+      <c r="R26" s="31">
         <v>295.0</v>
       </c>
-      <c r="S26" s="30">
+      <c r="S26" s="31">
         <v>305.0</v>
       </c>
-      <c r="T26" s="32">
+      <c r="T26" s="25">
         <v>320.0</v>
       </c>
-      <c r="U26" s="33"/>
-      <c r="V26" s="33"/>
-      <c r="W26" s="33"/>
-      <c r="X26" s="33"/>
-      <c r="Y26" s="33"/>
-      <c r="Z26" s="33"/>
-      <c r="AA26" s="33"/>
-      <c r="AB26" s="33"/>
-      <c r="AC26" s="33"/>
-      <c r="AR26" s="34"/>
+      <c r="U26" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V26" s="34"/>
+      <c r="W26" s="34"/>
+      <c r="X26" s="34"/>
+      <c r="Y26" s="34"/>
+      <c r="Z26" s="34"/>
+      <c r="AA26" s="34"/>
+      <c r="AB26" s="34"/>
+      <c r="AC26" s="34"/>
+      <c r="AR26" s="35"/>
     </row>
     <row r="27" ht="21.75" customHeight="1">
       <c r="A27" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27" s="24">
+        <v>150.0</v>
+      </c>
+      <c r="F27" s="25">
+        <v>250.0</v>
+      </c>
+      <c r="G27" s="26">
+        <v>0.5333</v>
+      </c>
+      <c r="H27" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="B27" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="C27" s="21" t="s">
+      <c r="I27" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="E27" s="23">
-        <v>150.0</v>
-      </c>
-      <c r="F27" s="24">
-        <v>230.0</v>
-      </c>
-      <c r="G27" s="25">
-        <v>0.5333</v>
-      </c>
-      <c r="H27" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="I27" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="J27" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="K27" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="L27" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="M27" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="N27" s="26">
+      <c r="J27" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="K27" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="L27" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="M27" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="N27" s="27">
         <v>250.0</v>
       </c>
-      <c r="O27" s="26">
+      <c r="O27" s="27">
         <v>210.0</v>
       </c>
       <c r="P27" s="42">
         <v>200.0</v>
       </c>
-      <c r="Q27" s="29">
+      <c r="Q27" s="30">
         <v>240.0</v>
       </c>
-      <c r="R27" s="30">
+      <c r="R27" s="31">
         <v>250.0</v>
       </c>
-      <c r="S27" s="30">
+      <c r="S27" s="31">
         <v>240.0</v>
       </c>
-      <c r="T27" s="32">
+      <c r="T27" s="25">
         <v>250.0</v>
       </c>
-      <c r="U27" s="33"/>
-      <c r="V27" s="33"/>
-      <c r="W27" s="33"/>
-      <c r="X27" s="33"/>
-      <c r="Y27" s="33"/>
-      <c r="Z27" s="33"/>
-      <c r="AA27" s="33"/>
-      <c r="AB27" s="33"/>
-      <c r="AC27" s="33"/>
-      <c r="AR27" s="34"/>
+      <c r="U27" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V27" s="34"/>
+      <c r="W27" s="34"/>
+      <c r="X27" s="34"/>
+      <c r="Y27" s="34"/>
+      <c r="Z27" s="34"/>
+      <c r="AA27" s="34"/>
+      <c r="AB27" s="34"/>
+      <c r="AC27" s="34"/>
+      <c r="AR27" s="35"/>
     </row>
     <row r="28" ht="21.75" customHeight="1">
       <c r="A28" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="B28" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="D28" s="38" t="s">
+      <c r="C28" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="E28" s="39">
+      <c r="D28" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="E28" s="40">
         <v>150.0</v>
       </c>
-      <c r="F28" s="40">
-        <v>220.0</v>
+      <c r="F28" s="25">
+        <v>230.0</v>
       </c>
       <c r="G28" s="41">
         <v>0.4667</v>
       </c>
-      <c r="H28" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="I28" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="J28" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="K28" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="L28" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="M28" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="N28" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="O28" s="26" t="s">
-        <v>90</v>
+      <c r="H28" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="I28" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="J28" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="K28" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="L28" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="M28" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="N28" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="O28" s="27" t="s">
+        <v>91</v>
       </c>
       <c r="P28" s="42">
         <v>210.0</v>
       </c>
-      <c r="Q28" s="29">
+      <c r="Q28" s="30">
         <v>230.0</v>
       </c>
-      <c r="R28" s="30">
+      <c r="R28" s="31">
         <v>230.0</v>
       </c>
-      <c r="S28" s="30">
+      <c r="S28" s="31">
         <v>250.0</v>
       </c>
-      <c r="T28" s="32">
+      <c r="T28" s="25">
         <v>230.0</v>
       </c>
-      <c r="U28" s="33"/>
-      <c r="V28" s="33"/>
-      <c r="W28" s="33"/>
-      <c r="X28" s="33"/>
-      <c r="Y28" s="33"/>
-      <c r="Z28" s="33"/>
-      <c r="AA28" s="33"/>
-      <c r="AB28" s="33"/>
-      <c r="AC28" s="33"/>
-      <c r="AR28" s="34"/>
+      <c r="U28" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V28" s="34"/>
+      <c r="W28" s="34"/>
+      <c r="X28" s="34"/>
+      <c r="Y28" s="34"/>
+      <c r="Z28" s="34"/>
+      <c r="AA28" s="34"/>
+      <c r="AB28" s="34"/>
+      <c r="AC28" s="34"/>
+      <c r="AR28" s="35"/>
     </row>
     <row r="29" ht="21.75" customHeight="1">
       <c r="A29" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C29" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="D29" s="54">
+        <v>46108.0</v>
+      </c>
+      <c r="E29" s="24">
+        <v>150.0</v>
+      </c>
+      <c r="F29" s="25">
+        <v>210.0</v>
+      </c>
+      <c r="G29" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="H29" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="B29" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="D29" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="E29" s="23">
+      <c r="I29" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="J29" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="K29" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="L29" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="M29" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="N29" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="O29" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="P29" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q29" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="R29" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="S29" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="T29" s="25">
+        <v>210.0</v>
+      </c>
+      <c r="U29" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="V29" s="34"/>
+      <c r="W29" s="34"/>
+      <c r="X29" s="34"/>
+      <c r="Y29" s="34"/>
+      <c r="Z29" s="34"/>
+      <c r="AA29" s="34"/>
+      <c r="AB29" s="34"/>
+      <c r="AC29" s="34"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="D30" s="54">
+        <v>46164.0</v>
+      </c>
+      <c r="E30" s="24">
         <v>150.0</v>
       </c>
-      <c r="F29" s="24">
-        <v>150.0</v>
-      </c>
-      <c r="G29" s="25">
+      <c r="F30" s="25">
+        <v>210.0</v>
+      </c>
+      <c r="G30" s="26">
         <v>0.0</v>
       </c>
-      <c r="H29" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="I29" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="J29" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="K29" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="L29" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="M29" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="N29" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="O29" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="P29" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q29" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="R29" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="S29" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="T29" s="32">
+      <c r="H30" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="I30" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="J30" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="K30" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="L30" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="M30" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="N30" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="O30" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="P30" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q30" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="R30" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="S30" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="T30" s="25">
         <v>210.0</v>
       </c>
-      <c r="U29" s="33"/>
-      <c r="V29" s="33"/>
-      <c r="W29" s="33"/>
-      <c r="X29" s="33"/>
-      <c r="Y29" s="33"/>
-      <c r="Z29" s="33"/>
-      <c r="AA29" s="33"/>
-      <c r="AB29" s="33"/>
-      <c r="AC29" s="33"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
+      <c r="U30" s="33" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="8"/>
@@ -3151,11 +3262,11 @@
       <c r="W34" s="8"/>
       <c r="X34" s="8"/>
       <c r="Y34" s="8"/>
-      <c r="Z34" s="53"/>
-      <c r="AA34" s="53"/>
-      <c r="AB34" s="53"/>
-      <c r="AC34" s="53"/>
-      <c r="AD34" s="53"/>
+      <c r="Z34" s="55"/>
+      <c r="AA34" s="55"/>
+      <c r="AB34" s="55"/>
+      <c r="AC34" s="55"/>
+      <c r="AD34" s="55"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="8"/>
@@ -3183,11 +3294,11 @@
       <c r="W35" s="8"/>
       <c r="X35" s="8"/>
       <c r="Y35" s="8"/>
-      <c r="Z35" s="54"/>
-      <c r="AA35" s="53"/>
-      <c r="AB35" s="55"/>
-      <c r="AC35" s="53"/>
-      <c r="AD35" s="56"/>
+      <c r="Z35" s="56"/>
+      <c r="AA35" s="55"/>
+      <c r="AB35" s="57"/>
+      <c r="AC35" s="55"/>
+      <c r="AD35" s="58"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="8"/>
@@ -3197,10 +3308,10 @@
       <c r="E36" s="8"/>
       <c r="F36" s="8"/>
       <c r="G36" s="8"/>
-      <c r="H36" s="53"/>
-      <c r="I36" s="53"/>
-      <c r="J36" s="53"/>
-      <c r="K36" s="53"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
+      <c r="J36" s="55"/>
+      <c r="K36" s="55"/>
       <c r="L36" s="8"/>
       <c r="M36" s="8"/>
       <c r="N36" s="8"/>
@@ -3215,11 +3326,11 @@
       <c r="W36" s="8"/>
       <c r="X36" s="8"/>
       <c r="Y36" s="8"/>
-      <c r="Z36" s="54"/>
-      <c r="AA36" s="53"/>
-      <c r="AB36" s="55"/>
-      <c r="AC36" s="54"/>
-      <c r="AD36" s="56"/>
+      <c r="Z36" s="56"/>
+      <c r="AA36" s="55"/>
+      <c r="AB36" s="57"/>
+      <c r="AC36" s="56"/>
+      <c r="AD36" s="58"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="8"/>
@@ -3229,10 +3340,10 @@
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
       <c r="G37" s="8"/>
-      <c r="H37" s="54"/>
-      <c r="I37" s="57"/>
-      <c r="J37" s="54"/>
-      <c r="K37" s="58"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="59"/>
+      <c r="J37" s="56"/>
+      <c r="K37" s="60"/>
       <c r="L37" s="8"/>
       <c r="M37" s="8"/>
       <c r="N37" s="8"/>
@@ -3247,11 +3358,11 @@
       <c r="W37" s="8"/>
       <c r="X37" s="8"/>
       <c r="Y37" s="8"/>
-      <c r="Z37" s="54"/>
-      <c r="AA37" s="53"/>
-      <c r="AB37" s="55"/>
-      <c r="AC37" s="54"/>
-      <c r="AD37" s="56"/>
+      <c r="Z37" s="56"/>
+      <c r="AA37" s="55"/>
+      <c r="AB37" s="57"/>
+      <c r="AC37" s="56"/>
+      <c r="AD37" s="58"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="8"/>
@@ -3261,10 +3372,10 @@
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
       <c r="G38" s="8"/>
-      <c r="H38" s="54"/>
-      <c r="I38" s="57"/>
-      <c r="J38" s="55"/>
-      <c r="K38" s="58"/>
+      <c r="H38" s="56"/>
+      <c r="I38" s="59"/>
+      <c r="J38" s="57"/>
+      <c r="K38" s="60"/>
       <c r="L38" s="8"/>
       <c r="M38" s="8"/>
       <c r="N38" s="8"/>
@@ -3279,11 +3390,11 @@
       <c r="W38" s="8"/>
       <c r="X38" s="8"/>
       <c r="Y38" s="8"/>
-      <c r="Z38" s="54"/>
-      <c r="AA38" s="53"/>
-      <c r="AB38" s="54"/>
-      <c r="AC38" s="53"/>
-      <c r="AD38" s="56"/>
+      <c r="Z38" s="56"/>
+      <c r="AA38" s="55"/>
+      <c r="AB38" s="56"/>
+      <c r="AC38" s="55"/>
+      <c r="AD38" s="58"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="8"/>
@@ -3293,10 +3404,10 @@
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
       <c r="G39" s="8"/>
-      <c r="H39" s="54"/>
-      <c r="I39" s="57"/>
-      <c r="J39" s="54"/>
-      <c r="K39" s="59"/>
+      <c r="H39" s="56"/>
+      <c r="I39" s="59"/>
+      <c r="J39" s="56"/>
+      <c r="K39" s="61"/>
       <c r="L39" s="8"/>
       <c r="M39" s="8"/>
       <c r="N39" s="8"/>
@@ -3311,11 +3422,11 @@
       <c r="W39" s="8"/>
       <c r="X39" s="8"/>
       <c r="Y39" s="8"/>
-      <c r="Z39" s="54"/>
-      <c r="AA39" s="53"/>
-      <c r="AB39" s="55"/>
-      <c r="AC39" s="53"/>
-      <c r="AD39" s="56"/>
+      <c r="Z39" s="56"/>
+      <c r="AA39" s="55"/>
+      <c r="AB39" s="57"/>
+      <c r="AC39" s="55"/>
+      <c r="AD39" s="58"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="8"/>
@@ -3325,10 +3436,10 @@
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
       <c r="G40" s="8"/>
-      <c r="H40" s="54"/>
-      <c r="I40" s="57"/>
-      <c r="J40" s="55"/>
-      <c r="K40" s="58"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="60"/>
       <c r="L40" s="8"/>
       <c r="M40" s="8"/>
       <c r="N40" s="8"/>
@@ -3343,11 +3454,11 @@
       <c r="W40" s="8"/>
       <c r="X40" s="8"/>
       <c r="Y40" s="8"/>
-      <c r="Z40" s="54"/>
-      <c r="AA40" s="53"/>
-      <c r="AB40" s="55"/>
-      <c r="AC40" s="53"/>
-      <c r="AD40" s="56"/>
+      <c r="Z40" s="56"/>
+      <c r="AA40" s="55"/>
+      <c r="AB40" s="57"/>
+      <c r="AC40" s="55"/>
+      <c r="AD40" s="58"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="8"/>
@@ -3357,10 +3468,10 @@
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
-      <c r="H41" s="54"/>
-      <c r="I41" s="57"/>
-      <c r="J41" s="54"/>
-      <c r="K41" s="58"/>
+      <c r="H41" s="56"/>
+      <c r="I41" s="59"/>
+      <c r="J41" s="56"/>
+      <c r="K41" s="60"/>
       <c r="L41" s="8"/>
       <c r="M41" s="8"/>
       <c r="N41" s="8"/>
@@ -3375,11 +3486,11 @@
       <c r="W41" s="8"/>
       <c r="X41" s="8"/>
       <c r="Y41" s="8"/>
-      <c r="Z41" s="54"/>
-      <c r="AA41" s="53"/>
-      <c r="AB41" s="55"/>
-      <c r="AC41" s="53"/>
-      <c r="AD41" s="56"/>
+      <c r="Z41" s="56"/>
+      <c r="AA41" s="55"/>
+      <c r="AB41" s="57"/>
+      <c r="AC41" s="55"/>
+      <c r="AD41" s="58"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="8"/>
@@ -3389,10 +3500,10 @@
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
       <c r="G42" s="8"/>
-      <c r="H42" s="54"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="55"/>
-      <c r="K42" s="58"/>
+      <c r="H42" s="56"/>
+      <c r="I42" s="59"/>
+      <c r="J42" s="57"/>
+      <c r="K42" s="60"/>
       <c r="L42" s="8"/>
       <c r="M42" s="8"/>
       <c r="N42" s="8"/>
@@ -3407,11 +3518,11 @@
       <c r="W42" s="8"/>
       <c r="X42" s="8"/>
       <c r="Y42" s="8"/>
-      <c r="Z42" s="54"/>
-      <c r="AA42" s="53"/>
-      <c r="AB42" s="55"/>
-      <c r="AC42" s="54"/>
-      <c r="AD42" s="56"/>
+      <c r="Z42" s="56"/>
+      <c r="AA42" s="55"/>
+      <c r="AB42" s="57"/>
+      <c r="AC42" s="56"/>
+      <c r="AD42" s="58"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="8"/>
@@ -3421,10 +3532,10 @@
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
       <c r="G43" s="8"/>
-      <c r="H43" s="54"/>
-      <c r="I43" s="57"/>
-      <c r="J43" s="55"/>
-      <c r="K43" s="58"/>
+      <c r="H43" s="56"/>
+      <c r="I43" s="59"/>
+      <c r="J43" s="57"/>
+      <c r="K43" s="60"/>
       <c r="L43" s="8"/>
       <c r="M43" s="8"/>
       <c r="N43" s="8"/>
@@ -3439,11 +3550,11 @@
       <c r="W43" s="8"/>
       <c r="X43" s="8"/>
       <c r="Y43" s="8"/>
-      <c r="Z43" s="54"/>
-      <c r="AA43" s="53"/>
-      <c r="AB43" s="55"/>
-      <c r="AC43" s="53"/>
-      <c r="AD43" s="56"/>
+      <c r="Z43" s="56"/>
+      <c r="AA43" s="55"/>
+      <c r="AB43" s="57"/>
+      <c r="AC43" s="55"/>
+      <c r="AD43" s="58"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="8"/>
@@ -3453,10 +3564,10 @@
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
       <c r="G44" s="8"/>
-      <c r="H44" s="54"/>
-      <c r="I44" s="57"/>
-      <c r="J44" s="55"/>
-      <c r="K44" s="58"/>
+      <c r="H44" s="56"/>
+      <c r="I44" s="59"/>
+      <c r="J44" s="57"/>
+      <c r="K44" s="60"/>
       <c r="L44" s="8"/>
       <c r="M44" s="8"/>
       <c r="N44" s="8"/>
@@ -3471,11 +3582,11 @@
       <c r="W44" s="8"/>
       <c r="X44" s="8"/>
       <c r="Y44" s="8"/>
-      <c r="Z44" s="54"/>
-      <c r="AA44" s="53"/>
-      <c r="AB44" s="55"/>
-      <c r="AC44" s="53"/>
-      <c r="AD44" s="56"/>
+      <c r="Z44" s="56"/>
+      <c r="AA44" s="55"/>
+      <c r="AB44" s="57"/>
+      <c r="AC44" s="55"/>
+      <c r="AD44" s="58"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="8"/>
@@ -3485,10 +3596,10 @@
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
-      <c r="H45" s="54"/>
-      <c r="I45" s="57"/>
-      <c r="J45" s="55"/>
-      <c r="K45" s="58"/>
+      <c r="H45" s="56"/>
+      <c r="I45" s="59"/>
+      <c r="J45" s="57"/>
+      <c r="K45" s="60"/>
       <c r="L45" s="8"/>
       <c r="M45" s="8"/>
       <c r="N45" s="8"/>
@@ -3513,10 +3624,10 @@
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
-      <c r="H46" s="54"/>
-      <c r="I46" s="57"/>
-      <c r="J46" s="55"/>
-      <c r="K46" s="58"/>
+      <c r="H46" s="56"/>
+      <c r="I46" s="59"/>
+      <c r="J46" s="57"/>
+      <c r="K46" s="60"/>
       <c r="L46" s="8"/>
       <c r="M46" s="8"/>
       <c r="N46" s="8"/>
@@ -3541,10 +3652,10 @@
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
       <c r="G47" s="8"/>
-      <c r="H47" s="54"/>
-      <c r="I47" s="57"/>
-      <c r="J47" s="55"/>
-      <c r="K47" s="59"/>
+      <c r="H47" s="56"/>
+      <c r="I47" s="59"/>
+      <c r="J47" s="57"/>
+      <c r="K47" s="61"/>
       <c r="L47" s="8"/>
       <c r="M47" s="8"/>
       <c r="N47" s="8"/>
@@ -3569,10 +3680,10 @@
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
       <c r="G48" s="8"/>
-      <c r="H48" s="54"/>
-      <c r="I48" s="57"/>
-      <c r="J48" s="55"/>
-      <c r="K48" s="58"/>
+      <c r="H48" s="56"/>
+      <c r="I48" s="59"/>
+      <c r="J48" s="57"/>
+      <c r="K48" s="60"/>
       <c r="L48" s="8"/>
       <c r="M48" s="8"/>
       <c r="N48" s="8"/>
@@ -3597,10 +3708,10 @@
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
-      <c r="H49" s="54"/>
-      <c r="I49" s="57"/>
-      <c r="J49" s="55"/>
-      <c r="K49" s="58"/>
+      <c r="H49" s="56"/>
+      <c r="I49" s="59"/>
+      <c r="J49" s="57"/>
+      <c r="K49" s="60"/>
       <c r="L49" s="8"/>
       <c r="M49" s="8"/>
       <c r="N49" s="8"/>
@@ -3625,10 +3736,10 @@
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
       <c r="G50" s="8"/>
-      <c r="H50" s="54"/>
-      <c r="I50" s="57"/>
-      <c r="J50" s="55"/>
-      <c r="K50" s="58"/>
+      <c r="H50" s="56"/>
+      <c r="I50" s="59"/>
+      <c r="J50" s="57"/>
+      <c r="K50" s="60"/>
       <c r="L50" s="8"/>
       <c r="M50" s="8"/>
       <c r="N50" s="8"/>
@@ -3644,12 +3755,12 @@
       <c r="X50" s="8"/>
       <c r="Y50" s="8"/>
       <c r="Z50" s="8"/>
-      <c r="AE50" s="53"/>
-      <c r="AF50" s="53"/>
-      <c r="AG50" s="53"/>
-      <c r="AH50" s="53"/>
-      <c r="AI50" s="53"/>
-      <c r="AJ50" s="53"/>
+      <c r="AE50" s="55"/>
+      <c r="AF50" s="55"/>
+      <c r="AG50" s="55"/>
+      <c r="AH50" s="55"/>
+      <c r="AI50" s="55"/>
+      <c r="AJ50" s="55"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="8"/>
@@ -3659,10 +3770,10 @@
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
       <c r="G51" s="8"/>
-      <c r="H51" s="54"/>
-      <c r="I51" s="57"/>
-      <c r="J51" s="55"/>
-      <c r="K51" s="58"/>
+      <c r="H51" s="56"/>
+      <c r="I51" s="59"/>
+      <c r="J51" s="57"/>
+      <c r="K51" s="60"/>
       <c r="L51" s="8"/>
       <c r="M51" s="8"/>
       <c r="N51" s="8"/>
@@ -3673,18 +3784,18 @@
       <c r="S51" s="8"/>
       <c r="T51" s="8"/>
       <c r="U51" s="8"/>
-      <c r="V51" s="53"/>
-      <c r="W51" s="53"/>
-      <c r="X51" s="53"/>
-      <c r="Y51" s="53"/>
-      <c r="Z51" s="53"/>
-      <c r="AA51" s="53"/>
-      <c r="AE51" s="54"/>
-      <c r="AF51" s="53"/>
-      <c r="AG51" s="60"/>
-      <c r="AH51" s="53"/>
-      <c r="AI51" s="55"/>
-      <c r="AJ51" s="53"/>
+      <c r="V51" s="55"/>
+      <c r="W51" s="55"/>
+      <c r="X51" s="55"/>
+      <c r="Y51" s="55"/>
+      <c r="Z51" s="55"/>
+      <c r="AA51" s="55"/>
+      <c r="AE51" s="56"/>
+      <c r="AF51" s="55"/>
+      <c r="AG51" s="62"/>
+      <c r="AH51" s="55"/>
+      <c r="AI51" s="57"/>
+      <c r="AJ51" s="55"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="8"/>
@@ -3694,10 +3805,10 @@
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
       <c r="G52" s="8"/>
-      <c r="H52" s="54"/>
-      <c r="I52" s="57"/>
-      <c r="J52" s="55"/>
-      <c r="K52" s="58"/>
+      <c r="H52" s="56"/>
+      <c r="I52" s="59"/>
+      <c r="J52" s="57"/>
+      <c r="K52" s="60"/>
       <c r="L52" s="8"/>
       <c r="M52" s="8"/>
       <c r="N52" s="8"/>
@@ -3708,18 +3819,18 @@
       <c r="S52" s="8"/>
       <c r="T52" s="8"/>
       <c r="U52" s="8"/>
-      <c r="V52" s="54"/>
-      <c r="W52" s="53"/>
-      <c r="X52" s="61"/>
-      <c r="Y52" s="62"/>
-      <c r="Z52" s="53"/>
-      <c r="AA52" s="53"/>
-      <c r="AE52" s="54"/>
-      <c r="AF52" s="53"/>
-      <c r="AG52" s="63"/>
-      <c r="AH52" s="53"/>
-      <c r="AI52" s="55"/>
-      <c r="AJ52" s="54"/>
+      <c r="V52" s="56"/>
+      <c r="W52" s="55"/>
+      <c r="X52" s="63"/>
+      <c r="Y52" s="64"/>
+      <c r="Z52" s="55"/>
+      <c r="AA52" s="55"/>
+      <c r="AE52" s="56"/>
+      <c r="AF52" s="55"/>
+      <c r="AG52" s="65"/>
+      <c r="AH52" s="55"/>
+      <c r="AI52" s="57"/>
+      <c r="AJ52" s="56"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="8"/>
@@ -3729,10 +3840,10 @@
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
       <c r="G53" s="8"/>
-      <c r="H53" s="54"/>
-      <c r="I53" s="57"/>
-      <c r="J53" s="55"/>
-      <c r="K53" s="58"/>
+      <c r="H53" s="56"/>
+      <c r="I53" s="59"/>
+      <c r="J53" s="57"/>
+      <c r="K53" s="60"/>
       <c r="L53" s="8"/>
       <c r="M53" s="8"/>
       <c r="N53" s="8"/>
@@ -3743,18 +3854,18 @@
       <c r="S53" s="8"/>
       <c r="T53" s="8"/>
       <c r="U53" s="8"/>
-      <c r="V53" s="54"/>
-      <c r="W53" s="53"/>
-      <c r="X53" s="61"/>
-      <c r="Y53" s="62"/>
-      <c r="Z53" s="53"/>
-      <c r="AA53" s="53"/>
-      <c r="AE53" s="54"/>
-      <c r="AF53" s="53"/>
-      <c r="AG53" s="63"/>
-      <c r="AH53" s="53"/>
-      <c r="AI53" s="55"/>
-      <c r="AJ53" s="53"/>
+      <c r="V53" s="56"/>
+      <c r="W53" s="55"/>
+      <c r="X53" s="63"/>
+      <c r="Y53" s="64"/>
+      <c r="Z53" s="55"/>
+      <c r="AA53" s="55"/>
+      <c r="AE53" s="56"/>
+      <c r="AF53" s="55"/>
+      <c r="AG53" s="65"/>
+      <c r="AH53" s="55"/>
+      <c r="AI53" s="57"/>
+      <c r="AJ53" s="55"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="8"/>
@@ -3778,18 +3889,18 @@
       <c r="S54" s="8"/>
       <c r="T54" s="8"/>
       <c r="U54" s="8"/>
-      <c r="V54" s="54"/>
-      <c r="W54" s="53"/>
-      <c r="X54" s="61"/>
-      <c r="Y54" s="62"/>
-      <c r="Z54" s="53"/>
-      <c r="AA54" s="53"/>
-      <c r="AE54" s="54"/>
-      <c r="AF54" s="53"/>
-      <c r="AG54" s="63"/>
-      <c r="AH54" s="53"/>
-      <c r="AI54" s="55"/>
-      <c r="AJ54" s="53"/>
+      <c r="V54" s="56"/>
+      <c r="W54" s="55"/>
+      <c r="X54" s="63"/>
+      <c r="Y54" s="64"/>
+      <c r="Z54" s="55"/>
+      <c r="AA54" s="55"/>
+      <c r="AE54" s="56"/>
+      <c r="AF54" s="55"/>
+      <c r="AG54" s="65"/>
+      <c r="AH54" s="55"/>
+      <c r="AI54" s="57"/>
+      <c r="AJ54" s="55"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="8"/>
@@ -3813,18 +3924,18 @@
       <c r="S55" s="8"/>
       <c r="T55" s="8"/>
       <c r="U55" s="8"/>
-      <c r="V55" s="54"/>
-      <c r="W55" s="53"/>
-      <c r="X55" s="61"/>
-      <c r="Y55" s="62"/>
-      <c r="Z55" s="53"/>
-      <c r="AA55" s="54"/>
-      <c r="AE55" s="54"/>
-      <c r="AF55" s="53"/>
-      <c r="AG55" s="60"/>
-      <c r="AH55" s="53"/>
-      <c r="AI55" s="55"/>
-      <c r="AJ55" s="53"/>
+      <c r="V55" s="56"/>
+      <c r="W55" s="55"/>
+      <c r="X55" s="63"/>
+      <c r="Y55" s="64"/>
+      <c r="Z55" s="55"/>
+      <c r="AA55" s="56"/>
+      <c r="AE55" s="56"/>
+      <c r="AF55" s="55"/>
+      <c r="AG55" s="62"/>
+      <c r="AH55" s="55"/>
+      <c r="AI55" s="57"/>
+      <c r="AJ55" s="55"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="8"/>
@@ -3848,18 +3959,18 @@
       <c r="S56" s="8"/>
       <c r="T56" s="8"/>
       <c r="U56" s="8"/>
-      <c r="V56" s="54"/>
-      <c r="W56" s="53"/>
-      <c r="X56" s="61"/>
-      <c r="Y56" s="62"/>
-      <c r="Z56" s="53"/>
-      <c r="AA56" s="53"/>
-      <c r="AE56" s="54"/>
-      <c r="AF56" s="53"/>
-      <c r="AG56" s="63"/>
-      <c r="AH56" s="53"/>
-      <c r="AI56" s="54"/>
-      <c r="AJ56" s="53"/>
+      <c r="V56" s="56"/>
+      <c r="W56" s="55"/>
+      <c r="X56" s="63"/>
+      <c r="Y56" s="64"/>
+      <c r="Z56" s="55"/>
+      <c r="AA56" s="55"/>
+      <c r="AE56" s="56"/>
+      <c r="AF56" s="55"/>
+      <c r="AG56" s="65"/>
+      <c r="AH56" s="55"/>
+      <c r="AI56" s="56"/>
+      <c r="AJ56" s="55"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="8"/>
@@ -3883,18 +3994,18 @@
       <c r="S57" s="8"/>
       <c r="T57" s="8"/>
       <c r="U57" s="8"/>
-      <c r="V57" s="54"/>
-      <c r="W57" s="53"/>
-      <c r="X57" s="61"/>
-      <c r="Y57" s="62"/>
-      <c r="Z57" s="53"/>
-      <c r="AA57" s="53"/>
-      <c r="AE57" s="54"/>
-      <c r="AF57" s="53"/>
-      <c r="AG57" s="63"/>
-      <c r="AH57" s="53"/>
-      <c r="AI57" s="55"/>
-      <c r="AJ57" s="53"/>
+      <c r="V57" s="56"/>
+      <c r="W57" s="55"/>
+      <c r="X57" s="63"/>
+      <c r="Y57" s="64"/>
+      <c r="Z57" s="55"/>
+      <c r="AA57" s="55"/>
+      <c r="AE57" s="56"/>
+      <c r="AF57" s="55"/>
+      <c r="AG57" s="65"/>
+      <c r="AH57" s="55"/>
+      <c r="AI57" s="57"/>
+      <c r="AJ57" s="55"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="8"/>
@@ -3918,18 +4029,18 @@
       <c r="S58" s="8"/>
       <c r="T58" s="8"/>
       <c r="U58" s="8"/>
-      <c r="V58" s="54"/>
-      <c r="W58" s="53"/>
-      <c r="X58" s="61"/>
-      <c r="Y58" s="62"/>
-      <c r="Z58" s="53"/>
-      <c r="AA58" s="53"/>
-      <c r="AE58" s="54"/>
-      <c r="AF58" s="53"/>
-      <c r="AG58" s="63"/>
-      <c r="AH58" s="53"/>
-      <c r="AI58" s="55"/>
-      <c r="AJ58" s="53"/>
+      <c r="V58" s="56"/>
+      <c r="W58" s="55"/>
+      <c r="X58" s="63"/>
+      <c r="Y58" s="64"/>
+      <c r="Z58" s="55"/>
+      <c r="AA58" s="55"/>
+      <c r="AE58" s="56"/>
+      <c r="AF58" s="55"/>
+      <c r="AG58" s="65"/>
+      <c r="AH58" s="55"/>
+      <c r="AI58" s="57"/>
+      <c r="AJ58" s="55"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="8"/>
@@ -3953,18 +4064,18 @@
       <c r="S59" s="8"/>
       <c r="T59" s="8"/>
       <c r="U59" s="8"/>
-      <c r="V59" s="54"/>
-      <c r="W59" s="53"/>
-      <c r="X59" s="61"/>
-      <c r="Y59" s="62"/>
-      <c r="Z59" s="53"/>
-      <c r="AA59" s="54"/>
-      <c r="AE59" s="54"/>
-      <c r="AF59" s="53"/>
-      <c r="AG59" s="60"/>
-      <c r="AH59" s="53"/>
-      <c r="AI59" s="54"/>
-      <c r="AJ59" s="53"/>
+      <c r="V59" s="56"/>
+      <c r="W59" s="55"/>
+      <c r="X59" s="63"/>
+      <c r="Y59" s="64"/>
+      <c r="Z59" s="55"/>
+      <c r="AA59" s="56"/>
+      <c r="AE59" s="56"/>
+      <c r="AF59" s="55"/>
+      <c r="AG59" s="62"/>
+      <c r="AH59" s="55"/>
+      <c r="AI59" s="56"/>
+      <c r="AJ59" s="55"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="8"/>
@@ -3988,18 +4099,18 @@
       <c r="S60" s="8"/>
       <c r="T60" s="8"/>
       <c r="U60" s="8"/>
-      <c r="V60" s="54"/>
-      <c r="W60" s="53"/>
-      <c r="X60" s="61"/>
-      <c r="Y60" s="62"/>
-      <c r="Z60" s="53"/>
-      <c r="AA60" s="53"/>
-      <c r="AE60" s="54"/>
-      <c r="AF60" s="53"/>
-      <c r="AG60" s="63"/>
-      <c r="AH60" s="53"/>
-      <c r="AI60" s="54"/>
-      <c r="AJ60" s="53"/>
+      <c r="V60" s="56"/>
+      <c r="W60" s="55"/>
+      <c r="X60" s="63"/>
+      <c r="Y60" s="64"/>
+      <c r="Z60" s="55"/>
+      <c r="AA60" s="55"/>
+      <c r="AE60" s="56"/>
+      <c r="AF60" s="55"/>
+      <c r="AG60" s="65"/>
+      <c r="AH60" s="55"/>
+      <c r="AI60" s="56"/>
+      <c r="AJ60" s="55"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="8"/>
@@ -4023,18 +4134,18 @@
       <c r="S61" s="8"/>
       <c r="T61" s="8"/>
       <c r="U61" s="8"/>
-      <c r="V61" s="54"/>
-      <c r="W61" s="53"/>
-      <c r="X61" s="61"/>
-      <c r="Y61" s="62"/>
-      <c r="Z61" s="53"/>
-      <c r="AA61" s="54"/>
-      <c r="AE61" s="54"/>
-      <c r="AF61" s="53"/>
-      <c r="AG61" s="63"/>
-      <c r="AH61" s="53"/>
-      <c r="AI61" s="54"/>
-      <c r="AJ61" s="53"/>
+      <c r="V61" s="56"/>
+      <c r="W61" s="55"/>
+      <c r="X61" s="63"/>
+      <c r="Y61" s="64"/>
+      <c r="Z61" s="55"/>
+      <c r="AA61" s="56"/>
+      <c r="AE61" s="56"/>
+      <c r="AF61" s="55"/>
+      <c r="AG61" s="65"/>
+      <c r="AH61" s="55"/>
+      <c r="AI61" s="56"/>
+      <c r="AJ61" s="55"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="8"/>
@@ -4063,12 +4174,12 @@
       <c r="X62" s="8"/>
       <c r="Y62" s="8"/>
       <c r="Z62" s="8"/>
-      <c r="AE62" s="54"/>
-      <c r="AF62" s="53"/>
-      <c r="AG62" s="63"/>
-      <c r="AH62" s="53"/>
-      <c r="AI62" s="54"/>
-      <c r="AJ62" s="53"/>
+      <c r="AE62" s="56"/>
+      <c r="AF62" s="55"/>
+      <c r="AG62" s="65"/>
+      <c r="AH62" s="55"/>
+      <c r="AI62" s="56"/>
+      <c r="AJ62" s="55"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="8"/>
